--- a/projects/critical_materials/excel_files/Material_limits.xlsx
+++ b/projects/critical_materials/excel_files/Material_limits.xlsx
@@ -1,30 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Paolo/Documents/PdM_code/EnergyScope-Quebec/projects/critical_materials/excel_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D032713B-B644-7046-86C7-A2219B82D1B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E93CD9CA-6F2C-EE4F-82CF-EE43B91D08DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="34600" windowHeight="19540" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table of content" sheetId="1" r:id="rId1"/>
     <sheet name="Materials" sheetId="3" r:id="rId2"/>
     <sheet name="Material_limits" sheetId="2" r:id="rId3"/>
-    <sheet name="MiningCapacity_Calcul" sheetId="4" r:id="rId4"/>
-    <sheet name="Reserves_Resources_RR" sheetId="6" r:id="rId5"/>
-    <sheet name="MiningCapacity_Results" sheetId="9" r:id="rId6"/>
-    <sheet name="Ref&amp;Hp" sheetId="17" r:id="rId7"/>
-    <sheet name="Calcul_Prod" sheetId="18" r:id="rId8"/>
+    <sheet name="RoE_Demand" sheetId="19" r:id="rId4"/>
+    <sheet name="MiningCapacity_Calcul" sheetId="4" r:id="rId5"/>
+    <sheet name="Reserves_Resources_RR" sheetId="6" r:id="rId6"/>
+    <sheet name="MiningCapacity_Results" sheetId="9" r:id="rId7"/>
+    <sheet name="Ref&amp;Hp" sheetId="17" r:id="rId8"/>
+    <sheet name="Calcul_Prod" sheetId="18" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">MiningCapacity_Results!$A$1:$G$33</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Reserves_Resources_RR!$A$1:$L$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">MiningCapacity_Results!$A$1:$G$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Reserves_Resources_RR!$A$1:$L$40</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1212" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1306" uniqueCount="283">
   <si>
     <t>Table of content</t>
   </si>
@@ -852,6 +853,48 @@
   <si>
     <t>Red sheet represent data used for the material limits in EnergyScope</t>
   </si>
+  <si>
+    <t>Demand from rest of economy [%]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source </t>
+  </si>
+  <si>
+    <t>IAI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bieuville </t>
+  </si>
+  <si>
+    <t>Charpentier-Poncelet</t>
+  </si>
+  <si>
+    <t>https://www.cobaltinstitute.org/wp-content/uploads/2025/05/Cobalt-Market-Report-2024.pdf</t>
+  </si>
+  <si>
+    <t>https://www.iea.org/data-and-statistics/data-tools/critical-minerals-data-explorer</t>
+  </si>
+  <si>
+    <t>Charpentier-Poncelet + hypothèse</t>
+  </si>
+  <si>
+    <t>https://www.iea.org/data-and-statistics/charts/total-neodymium-demand-by-sector-and-scenario-2020-2040</t>
+  </si>
+  <si>
+    <t>same as Nd</t>
+  </si>
+  <si>
+    <t>https://www.silverinstitute.org/all-world-silver-surveys/</t>
+  </si>
+  <si>
+    <t>Hypothèse</t>
+  </si>
+  <si>
+    <t>RoE_Demand</t>
+  </si>
+  <si>
+    <t>Material demand from the rest of economy in % until 2050. Most values are hypothesis</t>
+  </si>
 </sst>
 </file>
 
@@ -1013,7 +1056,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="25">
+  <fills count="27">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1158,8 +1201,20 @@
         <bgColor rgb="FFFFF8E5"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor rgb="FFFFF8E5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="30">
+  <borders count="32">
     <border>
       <left/>
       <right/>
@@ -1514,8 +1569,32 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="11">
+  <cellStyleXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="169" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
@@ -1527,8 +1606,9 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="220">
+  <cellXfs count="232">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1931,9 +2011,6 @@
     <xf numFmtId="0" fontId="8" fillId="20" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1989,9 +2066,37 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="11"/>
+    <xf numFmtId="10" fontId="20" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="11">
+  <cellStyles count="12">
     <cellStyle name="Comma 3" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Lien hypertexte" xfId="11" builtinId="8"/>
     <cellStyle name="Milliers 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
@@ -2363,22 +2468,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="197"/>
-      <c r="B1" s="198"/>
+      <c r="A1" s="196"/>
+      <c r="B1" s="197"/>
     </row>
     <row r="2" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="199"/>
-      <c r="B2" s="200"/>
+      <c r="A2" s="198"/>
+      <c r="B2" s="199"/>
     </row>
     <row r="3" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="201"/>
-      <c r="B3" s="202"/>
+      <c r="A3" s="200"/>
+      <c r="B3" s="201"/>
     </row>
     <row r="4" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="205" t="s">
+      <c r="A4" s="204" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="206"/>
+      <c r="B4" s="205"/>
     </row>
     <row r="5" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="190" t="s">
@@ -2389,10 +2494,10 @@
       </c>
     </row>
     <row r="6" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="207" t="s">
+      <c r="A6" s="206" t="s">
         <v>259</v>
       </c>
-      <c r="B6" s="206"/>
+      <c r="B6" s="205"/>
     </row>
     <row r="7" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="195" t="s">
@@ -2403,10 +2508,10 @@
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A8" s="208" t="s">
+      <c r="A8" s="207" t="s">
         <v>268</v>
       </c>
-      <c r="B8" s="209"/>
+      <c r="B8" s="208"/>
     </row>
     <row r="9" spans="1:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="192" t="s">
@@ -2417,95 +2522,108 @@
       </c>
     </row>
     <row r="10" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="196" t="s">
+      <c r="A10" s="229" t="s">
+        <v>268</v>
+      </c>
+      <c r="B10" s="230"/>
+    </row>
+    <row r="11" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="231" t="s">
+        <v>281</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="224" t="s">
         <v>262</v>
       </c>
-      <c r="B10" s="196"/>
-    </row>
-    <row r="11" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="203" t="s">
+      <c r="B12" s="225"/>
+    </row>
+    <row r="13" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="226" t="s">
         <v>2</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B13" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="203"/>
-      <c r="B12" s="4" t="s">
+    <row r="14" spans="1:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="227"/>
+      <c r="B14" s="4" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="203"/>
-      <c r="B13" s="4" t="s">
+    <row r="15" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="227"/>
+      <c r="B15" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="203"/>
-      <c r="B14" s="4" t="s">
+    <row r="16" spans="1:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="228"/>
+      <c r="B16" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="203" t="s">
+    <row r="17" spans="1:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="202" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B17" s="4" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="203"/>
-      <c r="B16" s="4" t="s">
+    <row r="18" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="202"/>
+      <c r="B18" s="4" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="158" t="s">
+    <row r="19" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="158" t="s">
         <v>263</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B19" s="4" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="204" t="s">
+    <row r="20" spans="1:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="203" t="s">
         <v>7</v>
       </c>
-      <c r="B18" s="204"/>
-    </row>
-    <row r="19" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="193" t="s">
+      <c r="B20" s="203"/>
+    </row>
+    <row r="21" spans="1:2" ht="63.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="193" t="s">
         <v>8</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B21" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="193" t="s">
+    <row r="22" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="193" t="s">
         <v>10</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B22" s="4" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="63.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="22" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="23" spans="1:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="24" spans="1:2" ht="48" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="A10:B10"/>
+  <mergeCells count="9">
     <mergeCell ref="A1:B3"/>
-    <mergeCell ref="A11:A14"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="A20:B20"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A13:A16"/>
+    <mergeCell ref="A12:B12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -2910,32 +3028,32 @@
         <v>12</v>
       </c>
       <c r="B2" s="152">
-        <f>MiningCapacity_Results!C2*0.003</f>
-        <v>177359.49647070031</v>
+        <f>MiningCapacity_Results!C2*0.003*(1-RoE_Demand!B2)</f>
+        <v>44339.874117675077</v>
       </c>
       <c r="C2" s="152">
-        <f>MiningCapacity_Results!D2*0.003</f>
-        <v>238693.40960334826</v>
+        <f>MiningCapacity_Results!D2*0.003*(1-RoE_Demand!C2)</f>
+        <v>59673.352400837066</v>
       </c>
       <c r="D2" s="152">
-        <f>MiningCapacity_Results!E2*0.003</f>
-        <v>321237.62708970002</v>
+        <f>MiningCapacity_Results!E2*0.003*(1-RoE_Demand!D2)</f>
+        <v>80309.406772425005</v>
       </c>
       <c r="E2" s="152">
-        <f>MiningCapacity_Results!F2*0.003</f>
-        <v>432327.03085394984</v>
+        <f>MiningCapacity_Results!F2*0.003*(1-RoE_Demand!E2)</f>
+        <v>108081.75771348746</v>
       </c>
       <c r="F2" s="152">
-        <f>MiningCapacity_Results!G2*0.003</f>
-        <v>581833.02902683208</v>
+        <f>MiningCapacity_Results!G2*0.003*(1-RoE_Demand!F2)</f>
+        <v>145458.25725670802</v>
       </c>
       <c r="G2" s="152">
-        <f>MiningCapacity_Results!H2*0.003</f>
-        <v>783040.72960198706</v>
+        <f>MiningCapacity_Results!H2*0.003*(1-RoE_Demand!G2)</f>
+        <v>195760.18240049676</v>
       </c>
       <c r="H2" s="152">
-        <f>MiningCapacity_Results!I2*0.003</f>
-        <v>1053829.455576225</v>
+        <f>MiningCapacity_Results!I2*0.003*(1-RoE_Demand!H2)</f>
+        <v>263457.36389405624</v>
       </c>
       <c r="J2" s="165"/>
     </row>
@@ -2944,32 +3062,32 @@
         <v>13</v>
       </c>
       <c r="B3" s="152">
-        <f>MiningCapacity_Results!C3*0.003</f>
-        <v>10385.256564000001</v>
+        <f>MiningCapacity_Results!C3*0.003*(1-RoE_Demand!B3)</f>
+        <v>103.85256564000011</v>
       </c>
       <c r="C3" s="152">
-        <f>MiningCapacity_Results!D3*0.003</f>
-        <v>13236.637148530481</v>
+        <f>MiningCapacity_Results!D3*0.003*(1-RoE_Demand!C3)</f>
+        <v>132.36637148530494</v>
       </c>
       <c r="D3" s="152">
-        <f>MiningCapacity_Results!E3*0.003</f>
-        <v>16870.89403349064</v>
+        <f>MiningCapacity_Results!E3*0.003*(1-RoE_Demand!D3)</f>
+        <v>168.70894033490654</v>
       </c>
       <c r="E3" s="152">
-        <f>MiningCapacity_Results!F3*0.003</f>
-        <v>21502.974078342046</v>
+        <f>MiningCapacity_Results!F3*0.003*(1-RoE_Demand!E3)</f>
+        <v>215.02974078342064</v>
       </c>
       <c r="F3" s="152">
-        <f>MiningCapacity_Results!G3*0.003</f>
-        <v>27406.840046293772</v>
+        <f>MiningCapacity_Results!G3*0.003*(1-RoE_Demand!F3)</f>
+        <v>274.06840046293797</v>
       </c>
       <c r="G3" s="152">
-        <f>MiningCapacity_Results!H3*0.003</f>
-        <v>34931.674036647768</v>
+        <f>MiningCapacity_Results!H3*0.003*(1-RoE_Demand!G3)</f>
+        <v>349.31674036647797</v>
       </c>
       <c r="H3" s="152">
-        <f>MiningCapacity_Results!I3*0.003</f>
-        <v>44522.529738616206</v>
+        <f>MiningCapacity_Results!I3*0.003*(1-RoE_Demand!H3)</f>
+        <v>445.22529738616242</v>
       </c>
       <c r="J3" s="165"/>
     </row>
@@ -2978,32 +3096,32 @@
         <v>14</v>
       </c>
       <c r="B4" s="152">
-        <f>MiningCapacity_Results!C4*0.003</f>
-        <v>8.02065450746076</v>
+        <f>MiningCapacity_Results!C4*0.003*(1-RoE_Demand!B4)</f>
+        <v>0.64165236059686048</v>
       </c>
       <c r="C4" s="152">
-        <f>MiningCapacity_Results!D4*0.003</f>
-        <v>9.6201345283134323</v>
+        <f>MiningCapacity_Results!D4*0.003*(1-RoE_Demand!C4)</f>
+        <v>0.76961076226507419</v>
       </c>
       <c r="D4" s="152">
-        <f>MiningCapacity_Results!E4*0.003</f>
-        <v>11.538583074082261</v>
+        <f>MiningCapacity_Results!E4*0.003*(1-RoE_Demand!D4)</f>
+        <v>0.92308664592658041</v>
       </c>
       <c r="E4" s="152">
-        <f>MiningCapacity_Results!F4*0.003</f>
-        <v>13.839608891710487</v>
+        <f>MiningCapacity_Results!F4*0.003*(1-RoE_Demand!E4)</f>
+        <v>1.1071687113368385</v>
       </c>
       <c r="F4" s="152">
-        <f>MiningCapacity_Results!G4*0.003</f>
-        <v>16.599505593172321</v>
+        <f>MiningCapacity_Results!G4*0.003*(1-RoE_Demand!F4)</f>
+        <v>1.3279604474537849</v>
       </c>
       <c r="G4" s="152">
-        <f>MiningCapacity_Results!H4*0.003</f>
-        <v>19.909781272995492</v>
+        <f>MiningCapacity_Results!H4*0.003*(1-RoE_Demand!G4)</f>
+        <v>1.5927825018396384</v>
       </c>
       <c r="H4" s="152">
-        <f>MiningCapacity_Results!I4*0.003</f>
-        <v>23.88019258245669</v>
+        <f>MiningCapacity_Results!I4*0.003*(1-RoE_Demand!H4)</f>
+        <v>1.9104154065965342</v>
       </c>
       <c r="J4" s="165"/>
     </row>
@@ -3012,32 +3130,32 @@
         <v>15</v>
       </c>
       <c r="B5" s="152">
-        <f>MiningCapacity_Results!C5*0.003</f>
-        <v>99031.891029142193</v>
+        <f>MiningCapacity_Results!C5*0.003*(1-RoE_Demand!B5)</f>
+        <v>19806.378205828434</v>
       </c>
       <c r="C5" s="152">
-        <f>MiningCapacity_Results!D5*0.003</f>
-        <v>137721.25743857585</v>
+        <f>MiningCapacity_Results!D5*0.003*(1-RoE_Demand!C5)</f>
+        <v>27544.251487715163</v>
       </c>
       <c r="D5" s="152">
-        <f>MiningCapacity_Results!E5*0.003</f>
-        <v>191525.6242545243</v>
+        <f>MiningCapacity_Results!E5*0.003*(1-RoE_Demand!D5)</f>
+        <v>38305.124850904853</v>
       </c>
       <c r="E5" s="152">
-        <f>MiningCapacity_Results!F5*0.003</f>
-        <v>266350.05683451309</v>
+        <f>MiningCapacity_Results!F5*0.003*(1-RoE_Demand!E5)</f>
+        <v>53270.011366902603</v>
       </c>
       <c r="F5" s="152">
-        <f>MiningCapacity_Results!G5*0.003</f>
-        <v>370406.586856863</v>
+        <f>MiningCapacity_Results!G5*0.003*(1-RoE_Demand!F5)</f>
+        <v>74081.317371372585</v>
       </c>
       <c r="G5" s="152">
-        <f>MiningCapacity_Results!H5*0.003</f>
-        <v>515115.4883071619</v>
+        <f>MiningCapacity_Results!H5*0.003*(1-RoE_Demand!G5)</f>
+        <v>103023.09766143236</v>
       </c>
       <c r="H5" s="152">
-        <f>MiningCapacity_Results!I5*0.003</f>
-        <v>716358.66021049803</v>
+        <f>MiningCapacity_Results!I5*0.003*(1-RoE_Demand!H5)</f>
+        <v>143271.73204209958</v>
       </c>
       <c r="J5" s="165"/>
     </row>
@@ -3046,32 +3164,32 @@
         <v>16</v>
       </c>
       <c r="B6" s="152">
-        <f>MiningCapacity_Results!C6*0.003</f>
-        <v>426</v>
+        <f>MiningCapacity_Results!C6*0.003*(1-RoE_Demand!B6)</f>
+        <v>183.18</v>
       </c>
       <c r="C6" s="152">
-        <f>MiningCapacity_Results!D6*0.003</f>
-        <v>753</v>
+        <f>MiningCapacity_Results!D6*0.003*(1-RoE_Demand!C6)</f>
+        <v>323.79000000000002</v>
       </c>
       <c r="D6" s="152">
-        <f>MiningCapacity_Results!E6*0.003</f>
-        <v>1080</v>
+        <f>MiningCapacity_Results!E6*0.003*(1-RoE_Demand!D6)</f>
+        <v>615.6</v>
       </c>
       <c r="E6" s="152">
-        <f>MiningCapacity_Results!F6*0.003</f>
-        <v>928.5</v>
+        <f>MiningCapacity_Results!F6*0.003*(1-RoE_Demand!E6)</f>
+        <v>529.245</v>
       </c>
       <c r="F6" s="152">
-        <f>MiningCapacity_Results!G6*0.003</f>
-        <v>777</v>
+        <f>MiningCapacity_Results!G6*0.003*(1-RoE_Demand!F6)</f>
+        <v>442.89000000000004</v>
       </c>
       <c r="G6" s="152">
-        <f>MiningCapacity_Results!H6*0.003</f>
-        <v>1136.4031429324755</v>
+        <f>MiningCapacity_Results!H6*0.003*(1-RoE_Demand!G6)</f>
+        <v>647.74979147151112</v>
       </c>
       <c r="H6" s="152">
-        <f>MiningCapacity_Results!I6*0.003</f>
-        <v>1662.0490389534209</v>
+        <f>MiningCapacity_Results!I6*0.003*(1-RoE_Demand!H6)</f>
+        <v>947.36795220345005</v>
       </c>
       <c r="J6" s="165"/>
     </row>
@@ -3093,32 +3211,32 @@
         <v>18</v>
       </c>
       <c r="B8" s="93">
-        <f>MiningCapacity_Results!C7*0.003</f>
-        <v>61800</v>
+        <f>MiningCapacity_Results!C7*0.003*(1-RoE_Demand!B8)</f>
+        <v>12359.999999999996</v>
       </c>
       <c r="C8" s="93">
-        <f>MiningCapacity_Results!D7*0.003</f>
-        <v>67350</v>
+        <f>MiningCapacity_Results!D7*0.003*(1-RoE_Demand!C8)</f>
+        <v>13469.999999999996</v>
       </c>
       <c r="D8" s="93">
-        <f>MiningCapacity_Results!E7*0.003</f>
-        <v>72900</v>
+        <f>MiningCapacity_Results!E7*0.003*(1-RoE_Demand!D8)</f>
+        <v>14579.999999999996</v>
       </c>
       <c r="E8" s="93">
-        <f>MiningCapacity_Results!F7*0.003</f>
-        <v>61350</v>
+        <f>MiningCapacity_Results!F7*0.003*(1-RoE_Demand!E8)</f>
+        <v>15337.5</v>
       </c>
       <c r="F8" s="93">
-        <f>MiningCapacity_Results!G7*0.003</f>
-        <v>49800</v>
+        <f>MiningCapacity_Results!G7*0.003*(1-RoE_Demand!F8)</f>
+        <v>12450</v>
       </c>
       <c r="G8" s="93">
-        <f>MiningCapacity_Results!H7*0.003</f>
-        <v>56714.243728402034</v>
+        <f>MiningCapacity_Results!H7*0.003*(1-RoE_Demand!G8)</f>
+        <v>14178.560932100509</v>
       </c>
       <c r="H8" s="93">
-        <f>MiningCapacity_Results!I7*0.003</f>
-        <v>64588.462684429498</v>
+        <f>MiningCapacity_Results!I7*0.003*(1-RoE_Demand!H8)</f>
+        <v>16147.115671107375</v>
       </c>
       <c r="J8" s="165"/>
     </row>
@@ -3127,32 +3245,32 @@
         <v>19</v>
       </c>
       <c r="B9" s="93">
-        <f>MiningCapacity_Results!C8*0.003</f>
-        <v>3.3859270242083097</v>
+        <f>MiningCapacity_Results!C8*0.003*(1-RoE_Demand!B9)</f>
+        <v>0.84648175605207743</v>
       </c>
       <c r="C9" s="93">
-        <f>MiningCapacity_Results!D8*0.003</f>
-        <v>4.3679322489771826</v>
+        <f>MiningCapacity_Results!D8*0.003*(1-RoE_Demand!C9)</f>
+        <v>1.3103796746931549</v>
       </c>
       <c r="D9" s="93">
-        <f>MiningCapacity_Results!E8*0.003</f>
-        <v>5.6347440435801603</v>
+        <f>MiningCapacity_Results!E8*0.003*(1-RoE_Demand!D9)</f>
+        <v>1.9721604152530561</v>
       </c>
       <c r="E9" s="93">
-        <f>MiningCapacity_Results!F8*0.003</f>
-        <v>7.2689635797571688</v>
+        <f>MiningCapacity_Results!F8*0.003*(1-RoE_Demand!E9)</f>
+        <v>2.9075854319028678</v>
       </c>
       <c r="F9" s="93">
-        <f>MiningCapacity_Results!G8*0.003</f>
-        <v>9.3771484765197002</v>
+        <f>MiningCapacity_Results!G8*0.003*(1-RoE_Demand!F9)</f>
+        <v>4.2197168144338644</v>
       </c>
       <c r="G9" s="93">
-        <f>MiningCapacity_Results!H8*0.003</f>
-        <v>12.096760781078681</v>
+        <f>MiningCapacity_Results!H8*0.003*(1-RoE_Demand!G9)</f>
+        <v>6.0483803905393403</v>
       </c>
       <c r="H9" s="93">
-        <f>MiningCapacity_Results!I8*0.003</f>
-        <v>15.605130041510639</v>
+        <f>MiningCapacity_Results!I8*0.003*(1-RoE_Demand!H9)</f>
+        <v>8.5828215228308515</v>
       </c>
       <c r="J9" s="165"/>
     </row>
@@ -3161,32 +3279,32 @@
         <v>20</v>
       </c>
       <c r="B10" s="93">
-        <f>MiningCapacity_Results!C9*0.003</f>
-        <v>2.3377409999999998</v>
+        <f>MiningCapacity_Results!C9*0.003*(1-RoE_Demand!B10)</f>
+        <v>0.11688705000000009</v>
       </c>
       <c r="C10" s="93">
-        <f>MiningCapacity_Results!D9*0.003</f>
-        <v>3.1461713703710434</v>
+        <f>MiningCapacity_Results!D9*0.003*(1-RoE_Demand!C10)</f>
+        <v>0.15730856851855232</v>
       </c>
       <c r="D10" s="93">
-        <f>MiningCapacity_Results!E9*0.003</f>
-        <v>4.2341706338479801</v>
+        <f>MiningCapacity_Results!E9*0.003*(1-RoE_Demand!D10)</f>
+        <v>0.2117085316923992</v>
       </c>
       <c r="E10" s="93">
-        <f>MiningCapacity_Results!F9*0.003</f>
-        <v>5.6984184413407242</v>
+        <f>MiningCapacity_Results!F9*0.003*(1-RoE_Demand!E10)</f>
+        <v>0.28492092206703645</v>
       </c>
       <c r="F10" s="93">
-        <f>MiningCapacity_Results!G9*0.003</f>
-        <v>7.6690279019534406</v>
+        <f>MiningCapacity_Results!G9*0.003*(1-RoE_Demand!F10)</f>
+        <v>0.3834513950976724</v>
       </c>
       <c r="G10" s="93">
-        <f>MiningCapacity_Results!H9*0.003</f>
-        <v>10.321107438207482</v>
+        <f>MiningCapacity_Results!H9*0.003*(1-RoE_Demand!G10)</f>
+        <v>0.51605537191037454</v>
       </c>
       <c r="H10" s="93">
-        <f>MiningCapacity_Results!I9*0.003</f>
-        <v>13.890320926318172</v>
+        <f>MiningCapacity_Results!I9*0.003*(1-RoE_Demand!H10)</f>
+        <v>0.69451604631590924</v>
       </c>
       <c r="J10" s="165"/>
     </row>
@@ -3195,32 +3313,32 @@
         <v>21</v>
       </c>
       <c r="B11" s="93">
-        <f>MiningCapacity_Results!C10*0.003</f>
-        <v>0.88919999999999999</v>
+        <f>MiningCapacity_Results!C10*0.003*(1-RoE_Demand!B11)</f>
+        <v>6.2243999999999959E-2</v>
       </c>
       <c r="C11" s="93">
-        <f>MiningCapacity_Results!D10*0.003</f>
-        <v>1.0665243858364957</v>
+        <f>MiningCapacity_Results!D10*0.003*(1-RoE_Demand!C11)</f>
+        <v>7.4656707008554646E-2</v>
       </c>
       <c r="D11" s="93">
-        <f>MiningCapacity_Results!E10*0.003</f>
-        <v>1.279210824993156</v>
+        <f>MiningCapacity_Results!E10*0.003*(1-RoE_Demand!D11)</f>
+        <v>8.9544757749520851E-2</v>
       </c>
       <c r="E11" s="93">
-        <f>MiningCapacity_Results!F10*0.003</f>
-        <v>1.5343112229883302</v>
+        <f>MiningCapacity_Results!F10*0.003*(1-RoE_Demand!E11)</f>
+        <v>0.10740178560918304</v>
       </c>
       <c r="F11" s="93">
-        <f>MiningCapacity_Results!G10*0.003</f>
-        <v>1.8402837773050742</v>
+        <f>MiningCapacity_Results!G10*0.003*(1-RoE_Demand!F11)</f>
+        <v>0.1288198644113551</v>
       </c>
       <c r="G11" s="93">
-        <f>MiningCapacity_Results!H10*0.003</f>
-        <v>2.2072734203274407</v>
+        <f>MiningCapacity_Results!H10*0.003*(1-RoE_Demand!G11)</f>
+        <v>0.15450913942292074</v>
       </c>
       <c r="H11" s="93">
-        <f>MiningCapacity_Results!I10*0.003</f>
-        <v>2.6474481882455523</v>
+        <f>MiningCapacity_Results!I10*0.003*(1-RoE_Demand!H11)</f>
+        <v>0.18532137317718853</v>
       </c>
       <c r="J11" s="165"/>
     </row>
@@ -3242,32 +3360,32 @@
         <v>23</v>
       </c>
       <c r="B13" s="93">
-        <f>MiningCapacity_Results!C11*0.003</f>
-        <v>0.2249694293478261</v>
+        <f>MiningCapacity_Results!C11*0.003*(1-RoE_Demand!B13)</f>
+        <v>1.1248471467391314E-2</v>
       </c>
       <c r="C13" s="93">
-        <f>MiningCapacity_Results!D11*0.003</f>
-        <v>0.31845550752020374</v>
+        <f>MiningCapacity_Results!D11*0.003*(1-RoE_Demand!C13)</f>
+        <v>1.5922775376010202E-2</v>
       </c>
       <c r="D13" s="93">
-        <f>MiningCapacity_Results!E11*0.003</f>
-        <v>0.45078973869447003</v>
+        <f>MiningCapacity_Results!E11*0.003*(1-RoE_Demand!D13)</f>
+        <v>2.2539486934723522E-2</v>
       </c>
       <c r="E13" s="93">
-        <f>MiningCapacity_Results!F11*0.003</f>
-        <v>0.63811547834303417</v>
+        <f>MiningCapacity_Results!F11*0.003*(1-RoE_Demand!E13)</f>
+        <v>3.1905773917151735E-2</v>
       </c>
       <c r="F13" s="93">
-        <f>MiningCapacity_Results!G11*0.003</f>
-        <v>0.903284455587264</v>
+        <f>MiningCapacity_Results!G11*0.003*(1-RoE_Demand!F13)</f>
+        <v>4.5164222779363238E-2</v>
       </c>
       <c r="G13" s="93">
-        <f>MiningCapacity_Results!H11*0.003</f>
-        <v>1.2786444388157596</v>
+        <f>MiningCapacity_Results!H11*0.003*(1-RoE_Demand!G13)</f>
+        <v>6.3932221940788042E-2</v>
       </c>
       <c r="H13" s="93">
-        <f>MiningCapacity_Results!I11*0.003</f>
-        <v>1.8099853161444361</v>
+        <f>MiningCapacity_Results!I11*0.003*(1-RoE_Demand!H13)</f>
+        <v>9.0499265807221882E-2</v>
       </c>
       <c r="J13" s="165"/>
     </row>
@@ -3276,32 +3394,32 @@
         <v>24</v>
       </c>
       <c r="B14" s="93">
-        <f>MiningCapacity_Results!C12*0.003</f>
-        <v>2.4180000000000001</v>
+        <f>MiningCapacity_Results!C12*0.003*(1-RoE_Demand!B14)</f>
+        <v>0.24179999999999996</v>
       </c>
       <c r="C14" s="93">
-        <f>MiningCapacity_Results!D12*0.003</f>
-        <v>2.8326881850838879</v>
+        <f>MiningCapacity_Results!D12*0.003*(1-RoE_Demand!C14)</f>
+        <v>0.2832688185083887</v>
       </c>
       <c r="D14" s="93">
-        <f>MiningCapacity_Results!E12*0.003</f>
-        <v>3.3184955971521304</v>
+        <f>MiningCapacity_Results!E12*0.003*(1-RoE_Demand!D14)</f>
+        <v>0.33184955971521296</v>
       </c>
       <c r="E14" s="93">
-        <f>MiningCapacity_Results!F12*0.003</f>
-        <v>3.7436486973969916</v>
+        <f>MiningCapacity_Results!F12*0.003*(1-RoE_Demand!E14)</f>
+        <v>0.37436486973969907</v>
       </c>
       <c r="F14" s="93">
-        <f>MiningCapacity_Results!G12*0.003</f>
-        <v>4.2232708042612801</v>
+        <f>MiningCapacity_Results!G12*0.003*(1-RoE_Demand!F14)</f>
+        <v>0.42232708042612793</v>
       </c>
       <c r="G14" s="93">
-        <f>MiningCapacity_Results!H12*0.003</f>
-        <v>5.0359832752130407</v>
+        <f>MiningCapacity_Results!H12*0.003*(1-RoE_Demand!G14)</f>
+        <v>0.50359832752130396</v>
       </c>
       <c r="H14" s="93">
-        <f>MiningCapacity_Results!I12*0.003</f>
-        <v>6.0050914856409605</v>
+        <f>MiningCapacity_Results!I12*0.003*(1-RoE_Demand!H14)</f>
+        <v>0.60050914856409587</v>
       </c>
       <c r="J14" s="165"/>
     </row>
@@ -3310,32 +3428,32 @@
         <v>25</v>
       </c>
       <c r="B15" s="93">
-        <f>MiningCapacity_Results!C13*0.003</f>
-        <v>1.8000000000000002E-2</v>
+        <f>MiningCapacity_Results!C13*0.003*(1-RoE_Demand!B15)</f>
+        <v>5.4000000000000055E-4</v>
       </c>
       <c r="C15" s="93">
-        <f>MiningCapacity_Results!D13*0.003</f>
-        <v>2.0968426012214714E-2</v>
+        <f>MiningCapacity_Results!D13*0.003*(1-RoE_Demand!C15)</f>
+        <v>6.2905278036644199E-4</v>
       </c>
       <c r="D15" s="93">
-        <f>MiningCapacity_Results!E13*0.003</f>
-        <v>2.4426382746095696E-2</v>
+        <f>MiningCapacity_Results!E13*0.003*(1-RoE_Demand!D15)</f>
+        <v>7.3279148238287149E-4</v>
       </c>
       <c r="E15" s="93">
-        <f>MiningCapacity_Results!F13*0.003</f>
-        <v>2.8454599964308092E-2</v>
+        <f>MiningCapacity_Results!F13*0.003*(1-RoE_Demand!E15)</f>
+        <v>8.5363799892924355E-4</v>
       </c>
       <c r="F15" s="93">
-        <f>MiningCapacity_Results!G13*0.003</f>
-        <v>3.3147120781042316E-2</v>
+        <f>MiningCapacity_Results!G13*0.003*(1-RoE_Demand!F15)</f>
+        <v>9.9441362343127035E-4</v>
       </c>
       <c r="G15" s="93">
-        <f>MiningCapacity_Results!H13*0.003</f>
-        <v>3.8613497200846142E-2</v>
+        <f>MiningCapacity_Results!H13*0.003*(1-RoE_Demand!G15)</f>
+        <v>1.1584049160253853E-3</v>
       </c>
       <c r="H15" s="93">
-        <f>MiningCapacity_Results!I13*0.003</f>
-        <v>4.4981347729377896E-2</v>
+        <f>MiningCapacity_Results!I13*0.003*(1-RoE_Demand!H15)</f>
+        <v>1.3494404318813381E-3</v>
       </c>
       <c r="J15" s="165"/>
     </row>
@@ -3344,32 +3462,32 @@
         <v>26</v>
       </c>
       <c r="B16" s="93">
-        <f>MiningCapacity_Results!C14*0.003</f>
-        <v>7410000</v>
+        <f>MiningCapacity_Results!C14*0.003*(1-RoE_Demand!B16)</f>
+        <v>889200</v>
       </c>
       <c r="C16" s="93">
-        <f>MiningCapacity_Results!D14*0.003</f>
-        <v>8942232.773932891</v>
+        <f>MiningCapacity_Results!D14*0.003*(1-RoE_Demand!C16)</f>
+        <v>1073067.9328719468</v>
       </c>
       <c r="D16" s="93">
-        <f>MiningCapacity_Results!E14*0.003</f>
-        <v>10791299.18801613</v>
+        <f>MiningCapacity_Results!E14*0.003*(1-RoE_Demand!D16)</f>
+        <v>1294955.9025619356</v>
       </c>
       <c r="E16" s="93">
-        <f>MiningCapacity_Results!F14*0.003</f>
-        <v>13022713.801942421</v>
+        <f>MiningCapacity_Results!F14*0.003*(1-RoE_Demand!E16)</f>
+        <v>1562725.6562330904</v>
       </c>
       <c r="F16" s="93">
-        <f>MiningCapacity_Results!G14*0.003</f>
-        <v>15715538.213937631</v>
+        <f>MiningCapacity_Results!G14*0.003*(1-RoE_Demand!F16)</f>
+        <v>1885864.5856725157</v>
       </c>
       <c r="G16" s="93">
-        <f>MiningCapacity_Results!H14*0.003</f>
-        <v>18965182.304543573</v>
+        <f>MiningCapacity_Results!H14*0.003*(1-RoE_Demand!G16)</f>
+        <v>2275821.8765452285</v>
       </c>
       <c r="H16" s="93">
-        <f>MiningCapacity_Results!I14*0.003</f>
-        <v>22886784.7189341</v>
+        <f>MiningCapacity_Results!I14*0.003*(1-RoE_Demand!H16)</f>
+        <v>2746414.1662720921</v>
       </c>
       <c r="J16" s="165"/>
     </row>
@@ -3378,32 +3496,32 @@
         <v>27</v>
       </c>
       <c r="B17" s="93">
-        <f>MiningCapacity_Results!C15*0.003</f>
-        <v>8961.2357510149504</v>
+        <f>MiningCapacity_Results!C15*0.003*(1-RoE_Demand!B17)</f>
+        <v>448.06178755074791</v>
       </c>
       <c r="C17" s="93">
-        <f>MiningCapacity_Results!D15*0.003</f>
-        <v>9741.5988335910461</v>
+        <f>MiningCapacity_Results!D15*0.003*(1-RoE_Demand!C17)</f>
+        <v>487.07994167955275</v>
       </c>
       <c r="D17" s="93">
-        <f>MiningCapacity_Results!E15*0.003</f>
-        <v>10589.91755951451</v>
+        <f>MiningCapacity_Results!E15*0.003*(1-RoE_Demand!D17)</f>
+        <v>529.49587797572599</v>
       </c>
       <c r="E17" s="93">
-        <f>MiningCapacity_Results!F15*0.003</f>
-        <v>11512.109647813657</v>
+        <f>MiningCapacity_Results!F15*0.003*(1-RoE_Demand!E17)</f>
+        <v>575.60548239068339</v>
       </c>
       <c r="F17" s="93">
-        <f>MiningCapacity_Results!G15*0.003</f>
-        <v>12514.608144821099</v>
+        <f>MiningCapacity_Results!G15*0.003*(1-RoE_Demand!F17)</f>
+        <v>625.73040724105545</v>
       </c>
       <c r="G17" s="93">
-        <f>MiningCapacity_Results!H15*0.003</f>
-        <v>13604.406299949249</v>
+        <f>MiningCapacity_Results!H15*0.003*(1-RoE_Demand!G17)</f>
+        <v>680.22031499746311</v>
       </c>
       <c r="H17" s="93">
-        <f>MiningCapacity_Results!I15*0.003</f>
-        <v>14789.106349341841</v>
+        <f>MiningCapacity_Results!I15*0.003*(1-RoE_Demand!H17)</f>
+        <v>739.45531746709264</v>
       </c>
       <c r="J17" s="165"/>
     </row>
@@ -3412,32 +3530,32 @@
         <v>28</v>
       </c>
       <c r="B18" s="93">
-        <f>MiningCapacity_Results!C16*0.003</f>
-        <v>147.19604400000003</v>
+        <f>MiningCapacity_Results!C16*0.003*(1-RoE_Demand!B18)</f>
+        <v>1.4719604400000017</v>
       </c>
       <c r="C18" s="93">
-        <f>MiningCapacity_Results!D16*0.003</f>
-        <v>174.8227257041948</v>
+        <f>MiningCapacity_Results!D16*0.003*(1-RoE_Demand!C18)</f>
+        <v>1.7482272570419495</v>
       </c>
       <c r="D18" s="93">
-        <f>MiningCapacity_Results!E16*0.003</f>
-        <v>207.63455723473203</v>
+        <f>MiningCapacity_Results!E16*0.003*(1-RoE_Demand!D18)</f>
+        <v>2.0763455723473223</v>
       </c>
       <c r="E18" s="93">
-        <f>MiningCapacity_Results!F16*0.003</f>
-        <v>246.60472020674345</v>
+        <f>MiningCapacity_Results!F16*0.003*(1-RoE_Demand!E18)</f>
+        <v>2.4660472020674367</v>
       </c>
       <c r="F18" s="93">
-        <f>MiningCapacity_Results!G16*0.003</f>
-        <v>292.8890490974282</v>
+        <f>MiningCapacity_Results!G16*0.003*(1-RoE_Demand!F18)</f>
+        <v>2.9288904909742848</v>
       </c>
       <c r="G18" s="93">
-        <f>MiningCapacity_Results!H16*0.003</f>
-        <v>347.86031268695052</v>
+        <f>MiningCapacity_Results!H16*0.003*(1-RoE_Demand!G18)</f>
+        <v>3.4786031268695083</v>
       </c>
       <c r="H18" s="93">
-        <f>MiningCapacity_Results!I16*0.003</f>
-        <v>413.14892965633095</v>
+        <f>MiningCapacity_Results!I16*0.003*(1-RoE_Demand!H18)</f>
+        <v>4.1314892965633128</v>
       </c>
       <c r="J18" s="165"/>
     </row>
@@ -3446,32 +3564,32 @@
         <v>29</v>
       </c>
       <c r="B19" s="93">
-        <f>MiningCapacity_Results!C17*0.003</f>
-        <v>146.02500000000001</v>
+        <f>MiningCapacity_Results!C17*0.003*(1-RoE_Demand!B19)</f>
+        <v>87.614999999999995</v>
       </c>
       <c r="C19" s="93">
-        <f>MiningCapacity_Results!D17*0.003</f>
-        <v>527.27326500000004</v>
+        <f>MiningCapacity_Results!D17*0.003*(1-RoE_Demand!C19)</f>
+        <v>316.36395900000002</v>
       </c>
       <c r="D19" s="93">
-        <f>MiningCapacity_Results!E17*0.003</f>
-        <v>908.5215300000001</v>
+        <f>MiningCapacity_Results!E17*0.003*(1-RoE_Demand!D19)</f>
+        <v>708.64679340000009</v>
       </c>
       <c r="E19" s="93">
-        <f>MiningCapacity_Results!F17*0.003</f>
-        <v>871.033815</v>
+        <f>MiningCapacity_Results!F17*0.003*(1-RoE_Demand!E19)</f>
+        <v>696.82705200000009</v>
       </c>
       <c r="F19" s="93">
-        <f>MiningCapacity_Results!G17*0.003</f>
-        <v>833.54610000000002</v>
+        <f>MiningCapacity_Results!G17*0.003*(1-RoE_Demand!F19)</f>
+        <v>666.83688000000006</v>
       </c>
       <c r="G19" s="93">
-        <f>MiningCapacity_Results!H17*0.003</f>
-        <v>1059.9646978052569</v>
+        <f>MiningCapacity_Results!H17*0.003*(1-RoE_Demand!G19)</f>
+        <v>900.96999313446838</v>
       </c>
       <c r="H19" s="93">
-        <f>MiningCapacity_Results!I17*0.003</f>
-        <v>1347.8860504456679</v>
+        <f>MiningCapacity_Results!I17*0.003*(1-RoE_Demand!H19)</f>
+        <v>1145.7031428788177</v>
       </c>
       <c r="J19" s="165"/>
     </row>
@@ -3480,32 +3598,32 @@
         <v>30</v>
       </c>
       <c r="B20" s="93">
-        <f>MiningCapacity_Results!C18*0.003</f>
-        <v>2822.4</v>
+        <f>MiningCapacity_Results!C18*0.003*(1-RoE_Demand!B20)</f>
+        <v>141.12000000000012</v>
       </c>
       <c r="C20" s="93">
-        <f>MiningCapacity_Results!D18*0.003</f>
-        <v>3706.2793887769185</v>
+        <f>MiningCapacity_Results!D18*0.003*(1-RoE_Demand!C20)</f>
+        <v>185.3139694388461</v>
       </c>
       <c r="D20" s="93">
-        <f>MiningCapacity_Results!E18*0.003</f>
-        <v>4866.9596469928438</v>
+        <f>MiningCapacity_Results!E18*0.003*(1-RoE_Demand!D20)</f>
+        <v>243.34798234964239</v>
       </c>
       <c r="E20" s="93">
-        <f>MiningCapacity_Results!F18*0.003</f>
-        <v>6391.1253633994338</v>
+        <f>MiningCapacity_Results!F18*0.003*(1-RoE_Demand!E20)</f>
+        <v>319.55626816997199</v>
       </c>
       <c r="F20" s="93">
-        <f>MiningCapacity_Results!G18*0.003</f>
-        <v>8392.6077825456032</v>
+        <f>MiningCapacity_Results!G18*0.003*(1-RoE_Demand!F20)</f>
+        <v>419.63038912728052</v>
       </c>
       <c r="G20" s="93">
-        <f>MiningCapacity_Results!H18*0.003</f>
-        <v>11020.886211216524</v>
+        <f>MiningCapacity_Results!H18*0.003*(1-RoE_Demand!G20)</f>
+        <v>551.04431056082672</v>
       </c>
       <c r="H20" s="93">
-        <f>MiningCapacity_Results!I18*0.003</f>
-        <v>14472.251775328637</v>
+        <f>MiningCapacity_Results!I18*0.003*(1-RoE_Demand!H20)</f>
+        <v>723.61258876643251</v>
       </c>
       <c r="J20" s="165"/>
     </row>
@@ -3514,32 +3632,32 @@
         <v>31</v>
       </c>
       <c r="B21" s="93">
-        <f>MiningCapacity_Results!C19*0.003</f>
-        <v>54674.741117340302</v>
+        <f>MiningCapacity_Results!C19*0.003*(1-RoE_Demand!B21)</f>
+        <v>2733.7370558670177</v>
       </c>
       <c r="C21" s="93">
-        <f>MiningCapacity_Results!D19*0.003</f>
-        <v>69318.132720072041</v>
+        <f>MiningCapacity_Results!D19*0.003*(1-RoE_Demand!C21)</f>
+        <v>4852.2692904050391</v>
       </c>
       <c r="D21" s="93">
-        <f>MiningCapacity_Results!E19*0.003</f>
-        <v>87883.425245402701</v>
+        <f>MiningCapacity_Results!E19*0.003*(1-RoE_Demand!D21)</f>
+        <v>8788.3425245402686</v>
       </c>
       <c r="E21" s="93">
-        <f>MiningCapacity_Results!F19*0.003</f>
-        <v>111421.01106580811</v>
+        <f>MiningCapacity_Results!F19*0.003*(1-RoE_Demand!E21)</f>
+        <v>13370.521327896973</v>
       </c>
       <c r="F21" s="93">
-        <f>MiningCapacity_Results!G19*0.003</f>
-        <v>141262.60637043571</v>
+        <f>MiningCapacity_Results!G19*0.003*(1-RoE_Demand!F21)</f>
+        <v>18364.138828156643</v>
       </c>
       <c r="G21" s="93">
-        <f>MiningCapacity_Results!H19*0.003</f>
-        <v>179096.59738038646</v>
+        <f>MiningCapacity_Results!H19*0.003*(1-RoE_Demand!G21)</f>
+        <v>26864.489607057974</v>
       </c>
       <c r="H21" s="93">
-        <f>MiningCapacity_Results!I19*0.003</f>
-        <v>227063.56634196453</v>
+        <f>MiningCapacity_Results!I19*0.003*(1-RoE_Demand!H21)</f>
+        <v>34059.534951294685</v>
       </c>
       <c r="J21" s="165"/>
     </row>
@@ -3548,32 +3666,32 @@
         <v>32</v>
       </c>
       <c r="B22" s="93">
-        <f>MiningCapacity_Results!C20*0.003</f>
-        <v>841.79100000000005</v>
+        <f>MiningCapacity_Results!C20*0.003*(1-RoE_Demand!B22)</f>
+        <v>126.26865000000002</v>
       </c>
       <c r="C22" s="93">
-        <f>MiningCapacity_Results!D20*0.003</f>
-        <v>947.64016275804033</v>
+        <f>MiningCapacity_Results!D20*0.003*(1-RoE_Demand!C22)</f>
+        <v>142.14602441370607</v>
       </c>
       <c r="D22" s="93">
-        <f>MiningCapacity_Results!E20*0.003</f>
-        <v>1066.7990962983511</v>
+        <f>MiningCapacity_Results!E20*0.003*(1-RoE_Demand!D22)</f>
+        <v>213.35981925967016</v>
       </c>
       <c r="E22" s="93">
-        <f>MiningCapacity_Results!F20*0.003</f>
-        <v>1200.9414085518852</v>
+        <f>MiningCapacity_Results!F20*0.003*(1-RoE_Demand!E22)</f>
+        <v>300.23535213797129</v>
       </c>
       <c r="F22" s="93">
-        <f>MiningCapacity_Results!G20*0.003</f>
-        <v>1351.951151607678</v>
+        <f>MiningCapacity_Results!G20*0.003*(1-RoE_Demand!F22)</f>
+        <v>337.98778790191949</v>
       </c>
       <c r="G22" s="93">
-        <f>MiningCapacity_Results!H20*0.003</f>
-        <v>1521.949283551879</v>
+        <f>MiningCapacity_Results!H20*0.003*(1-RoE_Demand!G22)</f>
+        <v>456.58478506556378</v>
       </c>
       <c r="H22" s="93">
-        <f>MiningCapacity_Results!I20*0.003</f>
-        <v>1713.323457692688</v>
+        <f>MiningCapacity_Results!I20*0.003*(1-RoE_Demand!H22)</f>
+        <v>513.99703730780641</v>
       </c>
       <c r="J22" s="165"/>
     </row>
@@ -3582,32 +3700,32 @@
         <v>33</v>
       </c>
       <c r="B23" s="93">
-        <f>MiningCapacity_Results!C21*0.003</f>
-        <v>98.6940532298253</v>
+        <f>MiningCapacity_Results!C21*0.003*(1-RoE_Demand!B23)</f>
+        <v>15.791048516772051</v>
       </c>
       <c r="C23" s="93">
-        <f>MiningCapacity_Results!D21*0.003</f>
-        <v>129.83320829586791</v>
+        <f>MiningCapacity_Results!D21*0.003*(1-RoE_Demand!C23)</f>
+        <v>38.949962488760377</v>
       </c>
       <c r="D23" s="93">
-        <f>MiningCapacity_Results!E21*0.003</f>
-        <v>170.79713949071191</v>
+        <f>MiningCapacity_Results!E21*0.003*(1-RoE_Demand!D23)</f>
+        <v>70.026827191191884</v>
       </c>
       <c r="E23" s="93">
-        <f>MiningCapacity_Results!F21*0.003</f>
-        <v>224.68568127602956</v>
+        <f>MiningCapacity_Results!F21*0.003*(1-RoE_Demand!E23)</f>
+        <v>92.121129323172127</v>
       </c>
       <c r="F23" s="93">
-        <f>MiningCapacity_Results!G21*0.003</f>
-        <v>295.57670298816032</v>
+        <f>MiningCapacity_Results!G21*0.003*(1-RoE_Demand!F23)</f>
+        <v>121.18644822514574</v>
       </c>
       <c r="G23" s="93">
-        <f>MiningCapacity_Results!H21*0.003</f>
-        <v>388.83469054719728</v>
+        <f>MiningCapacity_Results!H21*0.003*(1-RoE_Demand!G23)</f>
+        <v>194.41734527359864</v>
       </c>
       <c r="H23" s="93">
-        <f>MiningCapacity_Results!I21*0.003</f>
-        <v>511.51668938871302</v>
+        <f>MiningCapacity_Results!I21*0.003*(1-RoE_Demand!H23)</f>
+        <v>255.75834469435651</v>
       </c>
       <c r="J23" s="165"/>
     </row>
@@ -3616,32 +3734,32 @@
         <v>34</v>
       </c>
       <c r="B24" s="93">
-        <f>MiningCapacity_Results!C22*0.003</f>
-        <v>7113.1268814095101</v>
+        <f>MiningCapacity_Results!C22*0.003*(1-RoE_Demand!B24)</f>
+        <v>711.31268814095085</v>
       </c>
       <c r="C24" s="93">
-        <f>MiningCapacity_Results!D22*0.003</f>
-        <v>11094.77758594353</v>
+        <f>MiningCapacity_Results!D22*0.003*(1-RoE_Demand!C24)</f>
+        <v>1775.1644137509652</v>
       </c>
       <c r="D24" s="93">
-        <f>MiningCapacity_Results!E22*0.003</f>
-        <v>15076.42829047755</v>
+        <f>MiningCapacity_Results!E22*0.003*(1-RoE_Demand!D24)</f>
+        <v>4522.9284871432656</v>
       </c>
       <c r="E24" s="93">
-        <f>MiningCapacity_Results!F22*0.003</f>
-        <v>15742.398337143375</v>
+        <f>MiningCapacity_Results!F22*0.003*(1-RoE_Demand!E24)</f>
+        <v>5509.8394180001806</v>
       </c>
       <c r="F24" s="93">
-        <f>MiningCapacity_Results!G22*0.003</f>
-        <v>16408.3683838092</v>
+        <f>MiningCapacity_Results!G22*0.003*(1-RoE_Demand!F24)</f>
+        <v>6235.179985847496</v>
       </c>
       <c r="G24" s="93">
-        <f>MiningCapacity_Results!H22*0.003</f>
-        <v>21004.889598431011</v>
+        <f>MiningCapacity_Results!H22*0.003*(1-RoE_Demand!G24)</f>
+        <v>7981.8580474037844</v>
       </c>
       <c r="H24" s="93">
-        <f>MiningCapacity_Results!I22*0.003</f>
-        <v>26889.046901069731</v>
+        <f>MiningCapacity_Results!I22*0.003*(1-RoE_Demand!H24)</f>
+        <v>10217.837822406498</v>
       </c>
       <c r="J24" s="165"/>
     </row>
@@ -3650,32 +3768,32 @@
         <v>35</v>
       </c>
       <c r="B25" s="93">
-        <f>MiningCapacity_Results!C23*0.003</f>
-        <v>183.2718534005871</v>
+        <f>MiningCapacity_Results!C23*0.003*(1-RoE_Demand!B25)</f>
+        <v>18.327185340058705</v>
       </c>
       <c r="C25" s="93">
-        <f>MiningCapacity_Results!D23*0.003</f>
-        <v>191.42217382236132</v>
+        <f>MiningCapacity_Results!D23*0.003*(1-RoE_Demand!C25)</f>
+        <v>19.142217382236126</v>
       </c>
       <c r="D25" s="93">
-        <f>MiningCapacity_Results!E23*0.003</f>
-        <v>199.93494882592231</v>
+        <f>MiningCapacity_Results!E23*0.003*(1-RoE_Demand!D25)</f>
+        <v>19.993494882592227</v>
       </c>
       <c r="E25" s="93">
-        <f>MiningCapacity_Results!F23*0.003</f>
-        <v>208.82629720379117</v>
+        <f>MiningCapacity_Results!F23*0.003*(1-RoE_Demand!E25)</f>
+        <v>20.882629720379111</v>
       </c>
       <c r="F25" s="93">
-        <f>MiningCapacity_Results!G23*0.003</f>
-        <v>218.11305457063801</v>
+        <f>MiningCapacity_Results!G23*0.003*(1-RoE_Demand!F25)</f>
+        <v>21.811305457063796</v>
       </c>
       <c r="G25" s="93">
-        <f>MiningCapacity_Results!H23*0.003</f>
-        <v>227.81280524122812</v>
+        <f>MiningCapacity_Results!H23*0.003*(1-RoE_Demand!G25)</f>
+        <v>22.781280524122806</v>
       </c>
       <c r="H25" s="93">
-        <f>MiningCapacity_Results!I23*0.003</f>
-        <v>237.9439155260184</v>
+        <f>MiningCapacity_Results!I23*0.003*(1-RoE_Demand!H25)</f>
+        <v>23.794391552601834</v>
       </c>
       <c r="J25" s="165"/>
     </row>
@@ -3684,32 +3802,32 @@
         <v>36</v>
       </c>
       <c r="B26" s="93">
-        <f>MiningCapacity_Results!C24*0.003</f>
-        <v>0.61982009999999998</v>
+        <f>MiningCapacity_Results!C24*0.003*(1-RoE_Demand!B26)</f>
+        <v>0.46486507499999996</v>
       </c>
       <c r="C26" s="93">
-        <f>MiningCapacity_Results!D24*0.003</f>
-        <v>0.61982009999999998</v>
+        <f>MiningCapacity_Results!D24*0.003*(1-RoE_Demand!C26)</f>
+        <v>0.46486507499999996</v>
       </c>
       <c r="D26" s="93">
-        <f>MiningCapacity_Results!E24*0.003</f>
-        <v>0.61982009999999998</v>
+        <f>MiningCapacity_Results!E24*0.003*(1-RoE_Demand!D26)</f>
+        <v>0.43387406999999995</v>
       </c>
       <c r="E26" s="93">
-        <f>MiningCapacity_Results!F24*0.003</f>
-        <v>0.61982009999999998</v>
+        <f>MiningCapacity_Results!F24*0.003*(1-RoE_Demand!E26)</f>
+        <v>0.37189205999999997</v>
       </c>
       <c r="F26" s="93">
-        <f>MiningCapacity_Results!G24*0.003</f>
-        <v>0.61982009999999998</v>
+        <f>MiningCapacity_Results!G24*0.003*(1-RoE_Demand!F26)</f>
+        <v>0.30991004999999999</v>
       </c>
       <c r="G26" s="93">
-        <f>MiningCapacity_Results!H24*0.003</f>
-        <v>0.61982009999999998</v>
+        <f>MiningCapacity_Results!H24*0.003*(1-RoE_Demand!G26)</f>
+        <v>0.24792804000000002</v>
       </c>
       <c r="H26" s="93">
-        <f>MiningCapacity_Results!I24*0.003</f>
-        <v>0.61982009999999998</v>
+        <f>MiningCapacity_Results!I24*0.003*(1-RoE_Demand!H26)</f>
+        <v>0.21693703499999997</v>
       </c>
       <c r="J26" s="165"/>
     </row>
@@ -3731,32 +3849,32 @@
         <v>38</v>
       </c>
       <c r="B28" s="93">
-        <f>MiningCapacity_Results!C25*0.003</f>
-        <v>28.276360823546135</v>
+        <f>MiningCapacity_Results!C25*0.003*(1-RoE_Demand!B28)</f>
+        <v>4.5242177317673828</v>
       </c>
       <c r="C28" s="93">
-        <f>MiningCapacity_Results!D25*0.003</f>
-        <v>37.00598848898602</v>
+        <f>MiningCapacity_Results!D25*0.003*(1-RoE_Demand!C28)</f>
+        <v>11.101796546695807</v>
       </c>
       <c r="D28" s="93">
-        <f>MiningCapacity_Results!E25*0.003</f>
-        <v>48.430672977783303</v>
+        <f>MiningCapacity_Results!E25*0.003*(1-RoE_Demand!D28)</f>
+        <v>19.856575920891157</v>
       </c>
       <c r="E28" s="93">
-        <f>MiningCapacity_Results!F25*0.003</f>
-        <v>63.382446486440337</v>
+        <f>MiningCapacity_Results!F25*0.003*(1-RoE_Demand!E28)</f>
+        <v>25.98680305944054</v>
       </c>
       <c r="F28" s="93">
-        <f>MiningCapacity_Results!G25*0.003</f>
-        <v>82.950210591732898</v>
+        <f>MiningCapacity_Results!G25*0.003*(1-RoE_Demand!F28)</f>
+        <v>34.00958634261049</v>
       </c>
       <c r="G28" s="93">
-        <f>MiningCapacity_Results!H25*0.003</f>
-        <v>108.55903832435474</v>
+        <f>MiningCapacity_Results!H25*0.003*(1-RoE_Demand!G28)</f>
+        <v>54.279519162177372</v>
       </c>
       <c r="H28" s="93">
-        <f>MiningCapacity_Results!I25*0.003</f>
-        <v>142.07395879816201</v>
+        <f>MiningCapacity_Results!I25*0.003*(1-RoE_Demand!H28)</f>
+        <v>71.036979399081005</v>
       </c>
       <c r="J28" s="165"/>
     </row>
@@ -3765,32 +3883,32 @@
         <v>39</v>
       </c>
       <c r="B29" s="93">
-        <f>MiningCapacity_Results!C26*0.003</f>
-        <v>0.51</v>
+        <f>MiningCapacity_Results!C26*0.003*(1-RoE_Demand!B29)</f>
+        <v>0.18870000000000001</v>
       </c>
       <c r="C29" s="93">
-        <f>MiningCapacity_Results!D26*0.003</f>
-        <v>0.54134326580370429</v>
+        <f>MiningCapacity_Results!D26*0.003*(1-RoE_Demand!C29)</f>
+        <v>0.20029700834737058</v>
       </c>
       <c r="D29" s="93">
-        <f>MiningCapacity_Results!E26*0.003</f>
-        <v>0.57461280672749038</v>
+        <f>MiningCapacity_Results!E26*0.003*(1-RoE_Demand!D29)</f>
+        <v>0.21260673848917144</v>
       </c>
       <c r="E29" s="93">
-        <f>MiningCapacity_Results!F26*0.003</f>
-        <v>0.60992700660096555</v>
+        <f>MiningCapacity_Results!F26*0.003*(1-RoE_Demand!E29)</f>
+        <v>0.22567299244235725</v>
       </c>
       <c r="F29" s="93">
-        <f>MiningCapacity_Results!G26*0.003</f>
-        <v>0.64741152481420416</v>
+        <f>MiningCapacity_Results!G26*0.003*(1-RoE_Demand!F29)</f>
+        <v>0.23954226418125554</v>
       </c>
       <c r="G29" s="93">
-        <f>MiningCapacity_Results!H26*0.003</f>
-        <v>0.68719974345466128</v>
+        <f>MiningCapacity_Results!H26*0.003*(1-RoE_Demand!G29)</f>
+        <v>0.25426390507822466</v>
       </c>
       <c r="H29" s="93">
-        <f>MiningCapacity_Results!I26*0.003</f>
-        <v>0.7294332419239492</v>
+        <f>MiningCapacity_Results!I26*0.003*(1-RoE_Demand!H29)</f>
+        <v>0.26989029951186122</v>
       </c>
       <c r="J29" s="165"/>
     </row>
@@ -3799,32 +3917,32 @@
         <v>40</v>
       </c>
       <c r="B30" s="93">
-        <f>MiningCapacity_Results!C27*0.003</f>
-        <v>17.922000000000001</v>
+        <f>MiningCapacity_Results!C27*0.003*(1-RoE_Demand!B30)</f>
+        <v>1.7921999999999996</v>
       </c>
       <c r="C30" s="93">
-        <f>MiningCapacity_Results!D27*0.003</f>
-        <v>19.531500000000001</v>
+        <f>MiningCapacity_Results!D27*0.003*(1-RoE_Demand!C30)</f>
+        <v>1.9531499999999997</v>
       </c>
       <c r="D30" s="93">
-        <f>MiningCapacity_Results!E27*0.003</f>
-        <v>21.141000000000002</v>
+        <f>MiningCapacity_Results!E27*0.003*(1-RoE_Demand!D30)</f>
+        <v>2.1140999999999996</v>
       </c>
       <c r="E30" s="93">
-        <f>MiningCapacity_Results!F27*0.003</f>
-        <v>17.791499999999999</v>
+        <f>MiningCapacity_Results!F27*0.003*(1-RoE_Demand!E30)</f>
+        <v>1.7791499999999996</v>
       </c>
       <c r="F30" s="93">
-        <f>MiningCapacity_Results!G27*0.003</f>
-        <v>14.442</v>
+        <f>MiningCapacity_Results!G27*0.003*(1-RoE_Demand!F30)</f>
+        <v>1.4441999999999997</v>
       </c>
       <c r="G30" s="93">
-        <f>MiningCapacity_Results!H27*0.003</f>
-        <v>16.447130681236594</v>
+        <f>MiningCapacity_Results!H27*0.003*(1-RoE_Demand!G30)</f>
+        <v>1.644713068123659</v>
       </c>
       <c r="H30" s="93">
-        <f>MiningCapacity_Results!I27*0.003</f>
-        <v>18.730654178484571</v>
+        <f>MiningCapacity_Results!I27*0.003*(1-RoE_Demand!H30)</f>
+        <v>1.8730654178484567</v>
       </c>
       <c r="J30" s="165"/>
     </row>
@@ -3833,32 +3951,32 @@
         <v>41</v>
       </c>
       <c r="B31" s="93">
-        <f>MiningCapacity_Results!C28*0.003</f>
-        <v>9000</v>
+        <f>MiningCapacity_Results!C28*0.003*(1-RoE_Demand!B31)</f>
+        <v>1799.9999999999995</v>
       </c>
       <c r="C31" s="93">
-        <f>MiningCapacity_Results!D28*0.003</f>
-        <v>13223.952691200011</v>
+        <f>MiningCapacity_Results!D28*0.003*(1-RoE_Demand!C31)</f>
+        <v>5289.5810764800044</v>
       </c>
       <c r="D31" s="93">
-        <f>MiningCapacity_Results!E28*0.003</f>
-        <v>19430.324975455111</v>
+        <f>MiningCapacity_Results!E28*0.003*(1-RoE_Demand!D31)</f>
+        <v>8743.6462389547996</v>
       </c>
       <c r="E31" s="93">
-        <f>MiningCapacity_Results!F28*0.003</f>
-        <v>28549.522027784442</v>
+        <f>MiningCapacity_Results!F28*0.003*(1-RoE_Demand!E31)</f>
+        <v>12847.284912502997</v>
       </c>
       <c r="F31" s="93">
-        <f>MiningCapacity_Results!G28*0.003</f>
-        <v>41948.614294643703</v>
+        <f>MiningCapacity_Results!G28*0.003*(1-RoE_Demand!F31)</f>
+        <v>18876.876432589663</v>
       </c>
       <c r="G31" s="93">
-        <f>MiningCapacity_Results!H28*0.003</f>
-        <v>61636.276765973838</v>
+        <f>MiningCapacity_Results!H28*0.003*(1-RoE_Demand!G31)</f>
+        <v>27736.324544688225</v>
       </c>
       <c r="H31" s="93">
-        <f>MiningCapacity_Results!I28*0.003</f>
-        <v>90563.912001660894</v>
+        <f>MiningCapacity_Results!I28*0.003*(1-RoE_Demand!H31)</f>
+        <v>40753.7604007474</v>
       </c>
       <c r="J31" s="165"/>
     </row>
@@ -3867,32 +3985,32 @@
         <v>42</v>
       </c>
       <c r="B32" s="93">
-        <f>MiningCapacity_Results!C29*0.003</f>
-        <v>70.5</v>
+        <f>MiningCapacity_Results!C29*0.003*(1-RoE_Demand!B32)</f>
+        <v>7.049999999999998</v>
       </c>
       <c r="C32" s="93">
-        <f>MiningCapacity_Results!D29*0.003</f>
-        <v>79.364867852521442</v>
+        <f>MiningCapacity_Results!D29*0.003*(1-RoE_Demand!C32)</f>
+        <v>13.492027534928649</v>
       </c>
       <c r="D32" s="93">
-        <f>MiningCapacity_Results!E29*0.003</f>
-        <v>89.344429067350205</v>
+        <f>MiningCapacity_Results!E29*0.003*(1-RoE_Demand!D32)</f>
+        <v>16.08199723212304</v>
       </c>
       <c r="E32" s="93">
-        <f>MiningCapacity_Results!F29*0.003</f>
-        <v>100.57884831615921</v>
+        <f>MiningCapacity_Results!F29*0.003*(1-RoE_Demand!E32)</f>
+        <v>18.104192696908662</v>
       </c>
       <c r="F32" s="93">
-        <f>MiningCapacity_Results!G29*0.003</f>
-        <v>113.22591496979821</v>
+        <f>MiningCapacity_Results!G29*0.003*(1-RoE_Demand!F32)</f>
+        <v>20.380664694563684</v>
       </c>
       <c r="G32" s="93">
-        <f>MiningCapacity_Results!H29*0.003</f>
-        <v>127.46325927743055</v>
+        <f>MiningCapacity_Results!H29*0.003*(1-RoE_Demand!G32)</f>
+        <v>22.943386669937507</v>
       </c>
       <c r="H32" s="93">
-        <f>MiningCapacity_Results!I29*0.003</f>
-        <v>143.4908472142545</v>
+        <f>MiningCapacity_Results!I29*0.003*(1-RoE_Demand!H32)</f>
+        <v>25.828352498565817</v>
       </c>
       <c r="J32" s="165"/>
     </row>
@@ -3901,32 +4019,32 @@
         <v>43</v>
       </c>
       <c r="B33" s="93">
-        <f>MiningCapacity_Results!C30*0.003</f>
-        <v>4.2097990582934699</v>
+        <f>MiningCapacity_Results!C30*0.003*(1-RoE_Demand!B33)</f>
+        <v>4.2097990582934737E-2</v>
       </c>
       <c r="C33" s="93">
-        <f>MiningCapacity_Results!D30*0.003</f>
-        <v>6.1082003887364733</v>
+        <f>MiningCapacity_Results!D30*0.003*(1-RoE_Demand!C33)</f>
+        <v>6.1082003887364789E-2</v>
       </c>
       <c r="D33" s="93">
-        <f>MiningCapacity_Results!E30*0.003</f>
-        <v>8.8626823922766604</v>
+        <f>MiningCapacity_Results!E30*0.003*(1-RoE_Demand!D33)</f>
+        <v>8.862682392276669E-2</v>
       </c>
       <c r="E33" s="93">
-        <f>MiningCapacity_Results!F30*0.003</f>
-        <v>12.859293112127064</v>
+        <f>MiningCapacity_Results!F30*0.003*(1-RoE_Demand!E33)</f>
+        <v>0.12859293112127076</v>
       </c>
       <c r="F33" s="93">
-        <f>MiningCapacity_Results!G30*0.003</f>
-        <v>18.658168263786809</v>
+        <f>MiningCapacity_Results!G30*0.003*(1-RoE_Demand!F33)</f>
+        <v>0.18658168263786826</v>
       </c>
       <c r="G33" s="93">
-        <f>MiningCapacity_Results!H30*0.003</f>
-        <v>27.072035758441253</v>
+        <f>MiningCapacity_Results!H30*0.003*(1-RoE_Demand!G33)</f>
+        <v>0.27072035758441276</v>
       </c>
       <c r="H33" s="93">
-        <f>MiningCapacity_Results!I30*0.003</f>
-        <v>39.280121700305401</v>
+        <f>MiningCapacity_Results!I30*0.003*(1-RoE_Demand!H33)</f>
+        <v>0.39280121700305437</v>
       </c>
       <c r="J33" s="165"/>
     </row>
@@ -3935,32 +4053,32 @@
         <v>44</v>
       </c>
       <c r="B34" s="93">
-        <f>MiningCapacity_Results!C31*0.003</f>
-        <v>1.376663238571896</v>
+        <f>MiningCapacity_Results!C31*0.003*(1-RoE_Demand!B34)</f>
+        <v>0.55066529542875842</v>
       </c>
       <c r="C34" s="93">
-        <f>MiningCapacity_Results!D31*0.003</f>
-        <v>1.5002956167931589</v>
+        <f>MiningCapacity_Results!D31*0.003*(1-RoE_Demand!C34)</f>
+        <v>0.75014780839657946</v>
       </c>
       <c r="D34" s="93">
-        <f>MiningCapacity_Results!E31*0.003</f>
-        <v>1.6239279950144219</v>
+        <f>MiningCapacity_Results!E31*0.003*(1-RoE_Demand!D34)</f>
+        <v>0.97435679700865307</v>
       </c>
       <c r="E34" s="93">
-        <f>MiningCapacity_Results!F31*0.003</f>
-        <v>1.3666389916890913</v>
+        <f>MiningCapacity_Results!F31*0.003*(1-RoE_Demand!E34)</f>
+        <v>0.81998339501345474</v>
       </c>
       <c r="F34" s="93">
-        <f>MiningCapacity_Results!G31*0.003</f>
-        <v>1.109349988363761</v>
+        <f>MiningCapacity_Results!G31*0.003*(1-RoE_Demand!F34)</f>
+        <v>0.66560999301825652</v>
       </c>
       <c r="G34" s="93">
-        <f>MiningCapacity_Results!H31*0.003</f>
-        <v>1.2633724020112922</v>
+        <f>MiningCapacity_Results!H31*0.003*(1-RoE_Demand!G34)</f>
+        <v>0.75802344120677534</v>
       </c>
       <c r="H34" s="93">
-        <f>MiningCapacity_Results!I31*0.003</f>
-        <v>1.4387793238434781</v>
+        <f>MiningCapacity_Results!I31*0.003*(1-RoE_Demand!H34)</f>
+        <v>0.86326759430608679</v>
       </c>
       <c r="J34" s="165"/>
     </row>
@@ -3969,32 +4087,32 @@
         <v>45</v>
       </c>
       <c r="B35" s="93">
-        <f>MiningCapacity_Results!C32*0.003</f>
-        <v>0.94144014478053306</v>
+        <f>MiningCapacity_Results!C32*0.003*(1-RoE_Demand!B35)</f>
+        <v>0.28243204343415995</v>
       </c>
       <c r="C35" s="93">
-        <f>MiningCapacity_Results!D32*0.003</f>
-        <v>1.1781529329599465</v>
+        <f>MiningCapacity_Results!D32*0.003*(1-RoE_Demand!C35)</f>
+        <v>0.41235352653598123</v>
       </c>
       <c r="D35" s="93">
-        <f>MiningCapacity_Results!E32*0.003</f>
-        <v>1.474384049944782</v>
+        <f>MiningCapacity_Results!E32*0.003*(1-RoE_Demand!D35)</f>
+        <v>0.58975361997791287</v>
       </c>
       <c r="E35" s="93">
-        <f>MiningCapacity_Results!F32*0.003</f>
-        <v>1.8450985996106515</v>
+        <f>MiningCapacity_Results!F32*0.003*(1-RoE_Demand!E35)</f>
+        <v>0.73803943984426068</v>
       </c>
       <c r="F35" s="93">
-        <f>MiningCapacity_Results!G32*0.003</f>
-        <v>2.30902446510642</v>
+        <f>MiningCapacity_Results!G32*0.003*(1-RoE_Demand!F35)</f>
+        <v>0.92360978604256805</v>
       </c>
       <c r="G35" s="93">
-        <f>MiningCapacity_Results!H32*0.003</f>
-        <v>2.8895984103966326</v>
+        <f>MiningCapacity_Results!H32*0.003*(1-RoE_Demand!G35)</f>
+        <v>1.1558393641586531</v>
       </c>
       <c r="H35" s="93">
-        <f>MiningCapacity_Results!I32*0.003</f>
-        <v>3.6161500666394701</v>
+        <f>MiningCapacity_Results!I32*0.003*(1-RoE_Demand!H35)</f>
+        <v>1.4464600266557881</v>
       </c>
       <c r="J35" s="165"/>
     </row>
@@ -4003,32 +4121,32 @@
         <v>46</v>
       </c>
       <c r="B36" s="93">
-        <f>MiningCapacity_Results!C33*0.003</f>
-        <v>14777.996745599999</v>
+        <f>MiningCapacity_Results!C33*0.003*(1-RoE_Demand!B36)</f>
+        <v>147.77996745600012</v>
       </c>
       <c r="C36" s="93">
-        <f>MiningCapacity_Results!D33*0.003</f>
-        <v>18153.240501518678</v>
+        <f>MiningCapacity_Results!D33*0.003*(1-RoE_Demand!C36)</f>
+        <v>181.53240501518695</v>
       </c>
       <c r="D36" s="93">
-        <f>MiningCapacity_Results!E33*0.003</f>
-        <v>22299.378351405809</v>
+        <f>MiningCapacity_Results!E33*0.003*(1-RoE_Demand!D36)</f>
+        <v>668.98135054217482</v>
       </c>
       <c r="E36" s="93">
-        <f>MiningCapacity_Results!F33*0.003</f>
-        <v>27392.479861518146</v>
+        <f>MiningCapacity_Results!F33*0.003*(1-RoE_Demand!E36)</f>
+        <v>1369.6239930759086</v>
       </c>
       <c r="F36" s="93">
-        <f>MiningCapacity_Results!G33*0.003</f>
-        <v>33648.828282981005</v>
+        <f>MiningCapacity_Results!G33*0.003*(1-RoE_Demand!F36)</f>
+        <v>1682.4414141490518</v>
       </c>
       <c r="G36" s="93">
-        <f>MiningCapacity_Results!H33*0.003</f>
-        <v>41334.105219445752</v>
+        <f>MiningCapacity_Results!H33*0.003*(1-RoE_Demand!G36)</f>
+        <v>2066.7052609722896</v>
       </c>
       <c r="H36" s="93">
-        <f>MiningCapacity_Results!I33*0.003</f>
-        <v>50774.673041329799</v>
+        <f>MiningCapacity_Results!I33*0.003*(1-RoE_Demand!H36)</f>
+        <v>2538.7336520664921</v>
       </c>
       <c r="J36" s="165"/>
     </row>
@@ -4037,31 +4155,31 @@
         <v>47</v>
       </c>
       <c r="B37" s="93">
-        <f>MiningCapacity_Results!C34*0.003</f>
+        <f>MiningCapacity_Results!C34*0.003*(1-RoE_Demand!B37)</f>
         <v>275.61413950506028</v>
       </c>
       <c r="C37" s="93">
-        <f>MiningCapacity_Results!D34*0.003</f>
+        <f>MiningCapacity_Results!D34*0.003*(1-RoE_Demand!C37)</f>
         <v>305.6904119644995</v>
       </c>
       <c r="D37" s="93">
-        <f>MiningCapacity_Results!E34*0.003</f>
+        <f>MiningCapacity_Results!E34*0.003*(1-RoE_Demand!D37)</f>
         <v>339.048744505032</v>
       </c>
       <c r="E37" s="93">
-        <f>MiningCapacity_Results!F34*0.003</f>
+        <f>MiningCapacity_Results!F34*0.003*(1-RoE_Demand!E37)</f>
         <v>376.04729049790427</v>
       </c>
       <c r="F37" s="93">
-        <f>MiningCapacity_Results!G34*0.003</f>
+        <f>MiningCapacity_Results!G34*0.003*(1-RoE_Demand!F37)</f>
         <v>417.08328664439705</v>
       </c>
       <c r="G37" s="93">
-        <f>MiningCapacity_Results!H34*0.003</f>
+        <f>MiningCapacity_Results!H34*0.003*(1-RoE_Demand!G37)</f>
         <v>462.59731792712432</v>
       </c>
       <c r="H37" s="93">
-        <f>MiningCapacity_Results!I34*0.003</f>
+        <f>MiningCapacity_Results!I34*0.003*(1-RoE_Demand!H37)</f>
         <v>513.07804797227709</v>
       </c>
       <c r="J37" s="165"/>
@@ -4071,32 +4189,32 @@
         <v>48</v>
       </c>
       <c r="B38" s="93">
-        <f>MiningCapacity_Results!C35*0.003</f>
-        <v>912.16469492035196</v>
+        <f>MiningCapacity_Results!C35*0.003*(1-RoE_Demand!B38)</f>
+        <v>9.1216469492035284</v>
       </c>
       <c r="C38" s="93">
-        <f>MiningCapacity_Results!D35*0.003</f>
-        <v>1057.6927014063363</v>
+        <f>MiningCapacity_Results!D35*0.003*(1-RoE_Demand!C38)</f>
+        <v>10.576927014063372</v>
       </c>
       <c r="D38" s="93">
-        <f>MiningCapacity_Results!E35*0.003</f>
-        <v>1226.438445642666</v>
+        <f>MiningCapacity_Results!E35*0.003*(1-RoE_Demand!D38)</f>
+        <v>12.26438445642667</v>
       </c>
       <c r="E38" s="93">
-        <f>MiningCapacity_Results!F35*0.003</f>
-        <v>1422.1061173537828</v>
+        <f>MiningCapacity_Results!F35*0.003*(1-RoE_Demand!E38)</f>
+        <v>14.221061173537841</v>
       </c>
       <c r="F38" s="93">
-        <f>MiningCapacity_Results!G35*0.003</f>
-        <v>1648.9908777731612</v>
+        <f>MiningCapacity_Results!G35*0.003*(1-RoE_Demand!F38)</f>
+        <v>16.489908777731625</v>
       </c>
       <c r="G38" s="93">
-        <f>MiningCapacity_Results!H35*0.003</f>
-        <v>1912.0731440483924</v>
+        <f>MiningCapacity_Results!H35*0.003*(1-RoE_Demand!G38)</f>
+        <v>19.12073144048394</v>
       </c>
       <c r="H38" s="93">
-        <f>MiningCapacity_Results!I35*0.003</f>
-        <v>2217.127915909572</v>
+        <f>MiningCapacity_Results!I35*0.003*(1-RoE_Demand!H38)</f>
+        <v>22.171279159095739</v>
       </c>
       <c r="J38" s="165"/>
     </row>
@@ -4105,31 +4223,31 @@
         <v>49</v>
       </c>
       <c r="B39" s="93">
-        <f>MiningCapacity_Results!C36*0.003</f>
+        <f>MiningCapacity_Results!C36*0.003*(1-RoE_Demand!B39)</f>
         <v>315</v>
       </c>
       <c r="C39" s="93">
-        <f>MiningCapacity_Results!D36*0.003</f>
+        <f>MiningCapacity_Results!D36*0.003*(1-RoE_Demand!C39)</f>
         <v>386.09718191386088</v>
       </c>
       <c r="D39" s="93">
-        <f>MiningCapacity_Results!E36*0.003</f>
+        <f>MiningCapacity_Results!E36*0.003*(1-RoE_Demand!D39)</f>
         <v>473.24137740261904</v>
       </c>
       <c r="E39" s="93">
-        <f>MiningCapacity_Results!F36*0.003</f>
+        <f>MiningCapacity_Results!F36*0.003*(1-RoE_Demand!E39)</f>
         <v>580.05448311169732</v>
       </c>
       <c r="F39" s="93">
-        <f>MiningCapacity_Results!G36*0.003</f>
+        <f>MiningCapacity_Results!G36*0.003*(1-RoE_Demand!F39)</f>
         <v>710.97587709818106</v>
       </c>
       <c r="G39" s="93">
-        <f>MiningCapacity_Results!H36*0.003</f>
+        <f>MiningCapacity_Results!H36*0.003*(1-RoE_Demand!G39)</f>
         <v>871.44692875029637</v>
       </c>
       <c r="H39" s="93">
-        <f>MiningCapacity_Results!I36*0.003</f>
+        <f>MiningCapacity_Results!I36*0.003*(1-RoE_Demand!H39)</f>
         <v>1068.1371535808848</v>
       </c>
       <c r="J39" s="165"/>
@@ -4139,31 +4257,31 @@
         <v>50</v>
       </c>
       <c r="B40" s="93">
-        <f>MiningCapacity_Results!C37*0.003</f>
+        <f>MiningCapacity_Results!C37*0.003*(1-RoE_Demand!B40)</f>
         <v>17.205171220760729</v>
       </c>
       <c r="C40" s="93">
-        <f>MiningCapacity_Results!D37*0.003</f>
+        <f>MiningCapacity_Results!D37*0.003*(1-RoE_Demand!C40)</f>
         <v>21.500152916697488</v>
       </c>
       <c r="D40" s="93">
-        <f>MiningCapacity_Results!E37*0.003</f>
+        <f>MiningCapacity_Results!E37*0.003*(1-RoE_Demand!D40)</f>
         <v>26.867304574312563</v>
       </c>
       <c r="E40" s="93">
-        <f>MiningCapacity_Results!F37*0.003</f>
+        <f>MiningCapacity_Results!F37*0.003*(1-RoE_Demand!E40)</f>
         <v>33.57427539635173</v>
       </c>
       <c r="F40" s="93">
-        <f>MiningCapacity_Results!G37*0.003</f>
+        <f>MiningCapacity_Results!G37*0.003*(1-RoE_Demand!F40)</f>
         <v>41.955528708592503</v>
       </c>
       <c r="G40" s="93">
-        <f>MiningCapacity_Results!H37*0.003</f>
+        <f>MiningCapacity_Results!H37*0.003*(1-RoE_Demand!G40)</f>
         <v>52.429020982201344</v>
       </c>
       <c r="H40" s="93">
-        <f>MiningCapacity_Results!I37*0.003</f>
+        <f>MiningCapacity_Results!I37*0.003*(1-RoE_Demand!H40)</f>
         <v>65.517044493570012</v>
       </c>
       <c r="J40" s="165"/>
@@ -4173,31 +4291,31 @@
         <v>51</v>
       </c>
       <c r="B41" s="93">
-        <f>MiningCapacity_Results!C38*0.003</f>
+        <f>MiningCapacity_Results!C38*0.003*(1-RoE_Demand!B41)</f>
         <v>35124.578414664298</v>
       </c>
       <c r="C41" s="93">
-        <f>MiningCapacity_Results!D38*0.003</f>
+        <f>MiningCapacity_Results!D38*0.003*(1-RoE_Demand!C41)</f>
         <v>42129.126654819738</v>
       </c>
       <c r="D41" s="93">
-        <f>MiningCapacity_Results!E38*0.003</f>
+        <f>MiningCapacity_Results!E38*0.003*(1-RoE_Demand!D41)</f>
         <v>50530.522864776896</v>
       </c>
       <c r="E41" s="93">
-        <f>MiningCapacity_Results!F38*0.003</f>
+        <f>MiningCapacity_Results!F38*0.003*(1-RoE_Demand!E41)</f>
         <v>60607.326658067061</v>
       </c>
       <c r="F41" s="93">
-        <f>MiningCapacity_Results!G38*0.003</f>
+        <f>MiningCapacity_Results!G38*0.003*(1-RoE_Demand!F41)</f>
         <v>72693.648044519694</v>
       </c>
       <c r="G41" s="93">
-        <f>MiningCapacity_Results!H38*0.003</f>
+        <f>MiningCapacity_Results!H38*0.003*(1-RoE_Demand!G41)</f>
         <v>87190.225297903453</v>
       </c>
       <c r="H41" s="93">
-        <f>MiningCapacity_Results!I38*0.003</f>
+        <f>MiningCapacity_Results!I38*0.003*(1-RoE_Demand!H41)</f>
         <v>104577.7119734505</v>
       </c>
       <c r="J41" s="165"/>
@@ -4207,32 +4325,32 @@
         <v>52</v>
       </c>
       <c r="B42" s="93">
-        <f>MiningCapacity_Results!C39*0.003</f>
-        <v>1707.2133956041048</v>
+        <f>MiningCapacity_Results!C39*0.003*(1-RoE_Demand!B42)</f>
+        <v>17.072133956041064</v>
       </c>
       <c r="C42" s="93">
-        <f>MiningCapacity_Results!D39*0.003</f>
-        <v>2416.6461635186124</v>
+        <f>MiningCapacity_Results!D39*0.003*(1-RoE_Demand!C42)</f>
+        <v>24.166461635186145</v>
       </c>
       <c r="D42" s="93">
-        <f>MiningCapacity_Results!E39*0.003</f>
-        <v>3420.88381844184</v>
+        <f>MiningCapacity_Results!E39*0.003*(1-RoE_Demand!D42)</f>
+        <v>34.208838184418433</v>
       </c>
       <c r="E42" s="93">
-        <f>MiningCapacity_Results!F39*0.003</f>
-        <v>4842.4325728507065</v>
+        <f>MiningCapacity_Results!F39*0.003*(1-RoE_Demand!E42)</f>
+        <v>48.424325728507107</v>
       </c>
       <c r="F42" s="93">
-        <f>MiningCapacity_Results!G39*0.003</f>
-        <v>6854.7061131372302</v>
+        <f>MiningCapacity_Results!G39*0.003*(1-RoE_Demand!F42)</f>
+        <v>68.547061131372359</v>
       </c>
       <c r="G42" s="93">
-        <f>MiningCapacity_Results!H39*0.003</f>
-        <v>9703.1802075913965</v>
+        <f>MiningCapacity_Results!H39*0.003*(1-RoE_Demand!G42)</f>
+        <v>97.031802075914058</v>
       </c>
       <c r="H42" s="93">
-        <f>MiningCapacity_Results!I39*0.003</f>
-        <v>13735.338114722252</v>
+        <f>MiningCapacity_Results!I39*0.003*(1-RoE_Demand!H42)</f>
+        <v>137.35338114722265</v>
       </c>
       <c r="J42" s="165"/>
     </row>
@@ -4242,6 +4360,1173 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C118CF83-2C26-504D-AE05-F9F44E3772BC}">
+  <sheetPr>
+    <tabColor theme="5" tint="0.59999389629810485"/>
+  </sheetPr>
+  <dimension ref="A1:M42"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="14.83203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="20" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="153" t="s">
+        <v>269</v>
+      </c>
+      <c r="B1" s="154">
+        <v>2020</v>
+      </c>
+      <c r="C1" s="154">
+        <v>2025</v>
+      </c>
+      <c r="D1" s="154">
+        <v>2030</v>
+      </c>
+      <c r="E1" s="154">
+        <v>2035</v>
+      </c>
+      <c r="F1" s="154">
+        <v>2040</v>
+      </c>
+      <c r="G1" s="154">
+        <v>2045</v>
+      </c>
+      <c r="H1" s="154">
+        <v>2050</v>
+      </c>
+      <c r="K1" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="16" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="155" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="219">
+        <v>0.75</v>
+      </c>
+      <c r="C2" s="219">
+        <v>0.75</v>
+      </c>
+      <c r="D2" s="219">
+        <v>0.75</v>
+      </c>
+      <c r="E2" s="219">
+        <v>0.75</v>
+      </c>
+      <c r="F2" s="219">
+        <v>0.75</v>
+      </c>
+      <c r="G2" s="219">
+        <v>0.75</v>
+      </c>
+      <c r="H2" s="219">
+        <v>0.75</v>
+      </c>
+      <c r="K2" s="222" t="s">
+        <v>271</v>
+      </c>
+      <c r="L2" t="s">
+        <v>272</v>
+      </c>
+      <c r="M2" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A3" s="156" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="219">
+        <v>0.99</v>
+      </c>
+      <c r="C3" s="219">
+        <v>0.99</v>
+      </c>
+      <c r="D3" s="219">
+        <v>0.99</v>
+      </c>
+      <c r="E3" s="219">
+        <v>0.99</v>
+      </c>
+      <c r="F3" s="219">
+        <v>0.99</v>
+      </c>
+      <c r="G3" s="219">
+        <v>0.99</v>
+      </c>
+      <c r="H3" s="219">
+        <v>0.99</v>
+      </c>
+      <c r="K3" t="s">
+        <v>273</v>
+      </c>
+      <c r="L3" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A4" s="156" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="219">
+        <v>0.92</v>
+      </c>
+      <c r="C4" s="219">
+        <v>0.92</v>
+      </c>
+      <c r="D4" s="219">
+        <v>0.92</v>
+      </c>
+      <c r="E4" s="219">
+        <v>0.92</v>
+      </c>
+      <c r="F4" s="219">
+        <v>0.92</v>
+      </c>
+      <c r="G4" s="219">
+        <v>0.92</v>
+      </c>
+      <c r="H4" s="219">
+        <v>0.92</v>
+      </c>
+      <c r="K4" t="s">
+        <v>273</v>
+      </c>
+      <c r="L4" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A5" s="156" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="219">
+        <v>0.8</v>
+      </c>
+      <c r="C5" s="219">
+        <v>0.8</v>
+      </c>
+      <c r="D5" s="219">
+        <v>0.8</v>
+      </c>
+      <c r="E5" s="219">
+        <v>0.8</v>
+      </c>
+      <c r="F5" s="219">
+        <v>0.8</v>
+      </c>
+      <c r="G5" s="219">
+        <v>0.8</v>
+      </c>
+      <c r="H5" s="219">
+        <v>0.8</v>
+      </c>
+      <c r="K5" t="s">
+        <v>273</v>
+      </c>
+      <c r="L5" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A6" s="156" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="219">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="C6" s="219">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="D6" s="219">
+        <v>0.43</v>
+      </c>
+      <c r="E6" s="219">
+        <v>0.43</v>
+      </c>
+      <c r="F6" s="219">
+        <v>0.43</v>
+      </c>
+      <c r="G6" s="219">
+        <v>0.43</v>
+      </c>
+      <c r="H6" s="219">
+        <v>0.43</v>
+      </c>
+      <c r="K6" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A7" s="156" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="220"/>
+      <c r="C7" s="221"/>
+      <c r="D7" s="221"/>
+      <c r="E7" s="221"/>
+      <c r="F7" s="221"/>
+      <c r="G7" s="221"/>
+      <c r="H7" s="221"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A8" s="156" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="220">
+        <v>0.8</v>
+      </c>
+      <c r="C8" s="220">
+        <v>0.8</v>
+      </c>
+      <c r="D8" s="220">
+        <v>0.8</v>
+      </c>
+      <c r="E8" s="220">
+        <v>0.75</v>
+      </c>
+      <c r="F8" s="220">
+        <v>0.75</v>
+      </c>
+      <c r="G8" s="220">
+        <v>0.75</v>
+      </c>
+      <c r="H8" s="220">
+        <v>0.75</v>
+      </c>
+      <c r="K8" t="s">
+        <v>273</v>
+      </c>
+      <c r="L8" t="s">
+        <v>272</v>
+      </c>
+      <c r="M8" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A9" s="156" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="220">
+        <v>0.75</v>
+      </c>
+      <c r="C9" s="220">
+        <v>0.7</v>
+      </c>
+      <c r="D9" s="220">
+        <v>0.65</v>
+      </c>
+      <c r="E9" s="220">
+        <v>0.6</v>
+      </c>
+      <c r="F9" s="220">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G9" s="220">
+        <v>0.5</v>
+      </c>
+      <c r="H9" s="220">
+        <v>0.45</v>
+      </c>
+      <c r="K9" t="s">
+        <v>272</v>
+      </c>
+      <c r="L9" s="222" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A10" s="156" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="220">
+        <v>0.95</v>
+      </c>
+      <c r="C10" s="220">
+        <v>0.95</v>
+      </c>
+      <c r="D10" s="220">
+        <v>0.95</v>
+      </c>
+      <c r="E10" s="220">
+        <v>0.95</v>
+      </c>
+      <c r="F10" s="220">
+        <v>0.95</v>
+      </c>
+      <c r="G10" s="220">
+        <v>0.95</v>
+      </c>
+      <c r="H10" s="220">
+        <v>0.95</v>
+      </c>
+      <c r="K10" t="s">
+        <v>273</v>
+      </c>
+      <c r="L10" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A11" s="156" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="220">
+        <v>0.93</v>
+      </c>
+      <c r="C11" s="220">
+        <v>0.93</v>
+      </c>
+      <c r="D11" s="220">
+        <v>0.93</v>
+      </c>
+      <c r="E11" s="220">
+        <v>0.93</v>
+      </c>
+      <c r="F11" s="220">
+        <v>0.93</v>
+      </c>
+      <c r="G11" s="220">
+        <v>0.93</v>
+      </c>
+      <c r="H11" s="220">
+        <v>0.93</v>
+      </c>
+      <c r="K11" t="s">
+        <v>273</v>
+      </c>
+      <c r="L11" s="222" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A12" s="156" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="220"/>
+      <c r="C12" s="221"/>
+      <c r="D12" s="221"/>
+      <c r="E12" s="221"/>
+      <c r="F12" s="221"/>
+      <c r="G12" s="221"/>
+      <c r="H12" s="221"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A13" s="156" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="220">
+        <v>0.95</v>
+      </c>
+      <c r="C13" s="220">
+        <v>0.95</v>
+      </c>
+      <c r="D13" s="220">
+        <v>0.95</v>
+      </c>
+      <c r="E13" s="220">
+        <v>0.95</v>
+      </c>
+      <c r="F13" s="220">
+        <v>0.95</v>
+      </c>
+      <c r="G13" s="220">
+        <v>0.95</v>
+      </c>
+      <c r="H13" s="220">
+        <v>0.95</v>
+      </c>
+      <c r="K13" t="s">
+        <v>273</v>
+      </c>
+      <c r="L13" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A14" s="156" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="220">
+        <v>0.9</v>
+      </c>
+      <c r="C14" s="220">
+        <v>0.9</v>
+      </c>
+      <c r="D14" s="220">
+        <v>0.9</v>
+      </c>
+      <c r="E14" s="220">
+        <v>0.9</v>
+      </c>
+      <c r="F14" s="220">
+        <v>0.9</v>
+      </c>
+      <c r="G14" s="220">
+        <v>0.9</v>
+      </c>
+      <c r="H14" s="220">
+        <v>0.9</v>
+      </c>
+      <c r="K14" t="s">
+        <v>273</v>
+      </c>
+      <c r="L14" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A15" s="156" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="220">
+        <v>0.97</v>
+      </c>
+      <c r="C15" s="220">
+        <v>0.97</v>
+      </c>
+      <c r="D15" s="220">
+        <v>0.97</v>
+      </c>
+      <c r="E15" s="220">
+        <v>0.97</v>
+      </c>
+      <c r="F15" s="220">
+        <v>0.97</v>
+      </c>
+      <c r="G15" s="220">
+        <v>0.97</v>
+      </c>
+      <c r="H15" s="220">
+        <v>0.97</v>
+      </c>
+      <c r="K15" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A16" s="156" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" s="220">
+        <v>0.88</v>
+      </c>
+      <c r="C16" s="220">
+        <v>0.88</v>
+      </c>
+      <c r="D16" s="220">
+        <v>0.88</v>
+      </c>
+      <c r="E16" s="220">
+        <v>0.88</v>
+      </c>
+      <c r="F16" s="220">
+        <v>0.88</v>
+      </c>
+      <c r="G16" s="220">
+        <v>0.88</v>
+      </c>
+      <c r="H16" s="220">
+        <v>0.88</v>
+      </c>
+      <c r="K16" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A17" s="156" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" s="220">
+        <v>0.95</v>
+      </c>
+      <c r="C17" s="220">
+        <v>0.95</v>
+      </c>
+      <c r="D17" s="220">
+        <v>0.95</v>
+      </c>
+      <c r="E17" s="220">
+        <v>0.95</v>
+      </c>
+      <c r="F17" s="220">
+        <v>0.95</v>
+      </c>
+      <c r="G17" s="220">
+        <v>0.95</v>
+      </c>
+      <c r="H17" s="220">
+        <v>0.95</v>
+      </c>
+      <c r="K17" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A18" s="156" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" s="220">
+        <v>0.99</v>
+      </c>
+      <c r="C18" s="220">
+        <v>0.99</v>
+      </c>
+      <c r="D18" s="220">
+        <v>0.99</v>
+      </c>
+      <c r="E18" s="220">
+        <v>0.99</v>
+      </c>
+      <c r="F18" s="220">
+        <v>0.99</v>
+      </c>
+      <c r="G18" s="220">
+        <v>0.99</v>
+      </c>
+      <c r="H18" s="220">
+        <v>0.99</v>
+      </c>
+      <c r="K18" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A19" s="156" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" s="220">
+        <v>0.4</v>
+      </c>
+      <c r="C19" s="220">
+        <v>0.4</v>
+      </c>
+      <c r="D19" s="220">
+        <v>0.22</v>
+      </c>
+      <c r="E19" s="220">
+        <v>0.2</v>
+      </c>
+      <c r="F19" s="220">
+        <v>0.2</v>
+      </c>
+      <c r="G19" s="220">
+        <v>0.15</v>
+      </c>
+      <c r="H19" s="220">
+        <v>0.15</v>
+      </c>
+      <c r="K19" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A20" s="156" t="s">
+        <v>30</v>
+      </c>
+      <c r="B20" s="220">
+        <v>0.95</v>
+      </c>
+      <c r="C20" s="220">
+        <v>0.95</v>
+      </c>
+      <c r="D20" s="220">
+        <v>0.95</v>
+      </c>
+      <c r="E20" s="220">
+        <v>0.95</v>
+      </c>
+      <c r="F20" s="220">
+        <v>0.95</v>
+      </c>
+      <c r="G20" s="220">
+        <v>0.95</v>
+      </c>
+      <c r="H20" s="220">
+        <v>0.95</v>
+      </c>
+      <c r="K20" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A21" s="156" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" s="220">
+        <v>0.95</v>
+      </c>
+      <c r="C21" s="220">
+        <v>0.93</v>
+      </c>
+      <c r="D21" s="220">
+        <v>0.9</v>
+      </c>
+      <c r="E21" s="220">
+        <v>0.88</v>
+      </c>
+      <c r="F21" s="220">
+        <v>0.87</v>
+      </c>
+      <c r="G21" s="220">
+        <v>0.85</v>
+      </c>
+      <c r="H21" s="220">
+        <v>0.85</v>
+      </c>
+      <c r="K21" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A22" s="156" t="s">
+        <v>32</v>
+      </c>
+      <c r="B22" s="220">
+        <v>0.85</v>
+      </c>
+      <c r="C22" s="220">
+        <v>0.85</v>
+      </c>
+      <c r="D22" s="220">
+        <v>0.8</v>
+      </c>
+      <c r="E22" s="220">
+        <v>0.75</v>
+      </c>
+      <c r="F22" s="220">
+        <v>0.75</v>
+      </c>
+      <c r="G22" s="220">
+        <v>0.7</v>
+      </c>
+      <c r="H22" s="220">
+        <v>0.7</v>
+      </c>
+      <c r="K22" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A23" s="156" t="s">
+        <v>33</v>
+      </c>
+      <c r="B23" s="220">
+        <v>0.84</v>
+      </c>
+      <c r="C23" s="220">
+        <v>0.7</v>
+      </c>
+      <c r="D23" s="220">
+        <v>0.59</v>
+      </c>
+      <c r="E23" s="220">
+        <v>0.59</v>
+      </c>
+      <c r="F23" s="220">
+        <v>0.59</v>
+      </c>
+      <c r="G23" s="220">
+        <v>0.5</v>
+      </c>
+      <c r="H23" s="220">
+        <v>0.5</v>
+      </c>
+      <c r="K23" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A24" s="156" t="s">
+        <v>34</v>
+      </c>
+      <c r="B24" s="220">
+        <v>0.9</v>
+      </c>
+      <c r="C24" s="220">
+        <v>0.84</v>
+      </c>
+      <c r="D24" s="220">
+        <v>0.7</v>
+      </c>
+      <c r="E24" s="220">
+        <v>0.65</v>
+      </c>
+      <c r="F24" s="220">
+        <v>0.62</v>
+      </c>
+      <c r="G24" s="220">
+        <v>0.62</v>
+      </c>
+      <c r="H24" s="220">
+        <v>0.62</v>
+      </c>
+      <c r="K24" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A25" s="156" t="s">
+        <v>35</v>
+      </c>
+      <c r="B25" s="220">
+        <v>0.9</v>
+      </c>
+      <c r="C25" s="220">
+        <v>0.9</v>
+      </c>
+      <c r="D25" s="220">
+        <v>0.9</v>
+      </c>
+      <c r="E25" s="220">
+        <v>0.9</v>
+      </c>
+      <c r="F25" s="220">
+        <v>0.9</v>
+      </c>
+      <c r="G25" s="220">
+        <v>0.9</v>
+      </c>
+      <c r="H25" s="220">
+        <v>0.9</v>
+      </c>
+      <c r="K25" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A26" s="156" t="s">
+        <v>36</v>
+      </c>
+      <c r="B26" s="166">
+        <v>0.25</v>
+      </c>
+      <c r="C26" s="183">
+        <v>0.25</v>
+      </c>
+      <c r="D26" s="183">
+        <v>0.3</v>
+      </c>
+      <c r="E26" s="183">
+        <v>0.4</v>
+      </c>
+      <c r="F26" s="183">
+        <v>0.5</v>
+      </c>
+      <c r="G26" s="183">
+        <v>0.6</v>
+      </c>
+      <c r="H26" s="183">
+        <v>0.65</v>
+      </c>
+      <c r="K26" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A27" s="156" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" s="220"/>
+      <c r="C27" s="220"/>
+      <c r="D27" s="220"/>
+      <c r="E27" s="220"/>
+      <c r="F27" s="220"/>
+      <c r="G27" s="220"/>
+      <c r="H27" s="220"/>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A28" s="156" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" s="220">
+        <v>0.84</v>
+      </c>
+      <c r="C28" s="220">
+        <v>0.7</v>
+      </c>
+      <c r="D28" s="220">
+        <v>0.59</v>
+      </c>
+      <c r="E28" s="220">
+        <v>0.59</v>
+      </c>
+      <c r="F28" s="220">
+        <v>0.59</v>
+      </c>
+      <c r="G28" s="220">
+        <v>0.5</v>
+      </c>
+      <c r="H28" s="220">
+        <v>0.5</v>
+      </c>
+      <c r="K28" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A29" s="156" t="s">
+        <v>39</v>
+      </c>
+      <c r="B29" s="220">
+        <v>0.63</v>
+      </c>
+      <c r="C29" s="220">
+        <v>0.63</v>
+      </c>
+      <c r="D29" s="220">
+        <v>0.63</v>
+      </c>
+      <c r="E29" s="220">
+        <v>0.63</v>
+      </c>
+      <c r="F29" s="220">
+        <v>0.63</v>
+      </c>
+      <c r="G29" s="220">
+        <v>0.63</v>
+      </c>
+      <c r="H29" s="220">
+        <v>0.63</v>
+      </c>
+      <c r="K29" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A30" s="156" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30" s="220">
+        <v>0.9</v>
+      </c>
+      <c r="C30" s="220">
+        <v>0.9</v>
+      </c>
+      <c r="D30" s="220">
+        <v>0.9</v>
+      </c>
+      <c r="E30" s="220">
+        <v>0.9</v>
+      </c>
+      <c r="F30" s="220">
+        <v>0.9</v>
+      </c>
+      <c r="G30" s="220">
+        <v>0.9</v>
+      </c>
+      <c r="H30" s="220">
+        <v>0.9</v>
+      </c>
+      <c r="K30" t="s">
+        <v>276</v>
+      </c>
+      <c r="L30" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A31" s="156" t="s">
+        <v>41</v>
+      </c>
+      <c r="B31" s="220">
+        <v>0.8</v>
+      </c>
+      <c r="C31" s="220">
+        <v>0.6</v>
+      </c>
+      <c r="D31" s="220">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="E31" s="220">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="F31" s="220">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G31" s="220">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="H31" s="220">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="K31" t="s">
+        <v>276</v>
+      </c>
+      <c r="L31" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A32" s="156" t="s">
+        <v>42</v>
+      </c>
+      <c r="B32" s="166">
+        <v>0.9</v>
+      </c>
+      <c r="C32" s="183">
+        <v>0.83</v>
+      </c>
+      <c r="D32" s="183">
+        <v>0.82</v>
+      </c>
+      <c r="E32" s="183">
+        <v>0.82</v>
+      </c>
+      <c r="F32" s="183">
+        <v>0.82</v>
+      </c>
+      <c r="G32" s="183">
+        <v>0.82</v>
+      </c>
+      <c r="H32" s="183">
+        <v>0.82</v>
+      </c>
+      <c r="K32" s="222" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A33" s="156" t="s">
+        <v>43</v>
+      </c>
+      <c r="B33" s="220">
+        <v>0.99</v>
+      </c>
+      <c r="C33" s="220">
+        <v>0.99</v>
+      </c>
+      <c r="D33" s="220">
+        <v>0.99</v>
+      </c>
+      <c r="E33" s="220">
+        <v>0.99</v>
+      </c>
+      <c r="F33" s="220">
+        <v>0.99</v>
+      </c>
+      <c r="G33" s="220">
+        <v>0.99</v>
+      </c>
+      <c r="H33" s="220">
+        <v>0.99</v>
+      </c>
+      <c r="I33" s="165"/>
+      <c r="K33" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A34" s="156" t="s">
+        <v>44</v>
+      </c>
+      <c r="B34" s="223">
+        <v>0.6</v>
+      </c>
+      <c r="C34" s="183">
+        <v>0.5</v>
+      </c>
+      <c r="D34" s="183">
+        <v>0.4</v>
+      </c>
+      <c r="E34" s="183">
+        <v>0.4</v>
+      </c>
+      <c r="F34" s="183">
+        <v>0.4</v>
+      </c>
+      <c r="G34" s="183">
+        <v>0.4</v>
+      </c>
+      <c r="H34" s="183">
+        <v>0.4</v>
+      </c>
+      <c r="I34" s="165"/>
+      <c r="K34" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A35" s="156" t="s">
+        <v>45</v>
+      </c>
+      <c r="B35" s="166">
+        <v>0.7</v>
+      </c>
+      <c r="C35" s="183">
+        <v>0.65</v>
+      </c>
+      <c r="D35" s="183">
+        <v>0.6</v>
+      </c>
+      <c r="E35" s="183">
+        <v>0.6</v>
+      </c>
+      <c r="F35" s="183">
+        <v>0.6</v>
+      </c>
+      <c r="G35" s="183">
+        <v>0.6</v>
+      </c>
+      <c r="H35" s="183">
+        <v>0.6</v>
+      </c>
+      <c r="I35" s="165"/>
+      <c r="K35" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A36" s="156" t="s">
+        <v>46</v>
+      </c>
+      <c r="B36" s="220">
+        <v>0.99</v>
+      </c>
+      <c r="C36" s="220">
+        <v>0.99</v>
+      </c>
+      <c r="D36" s="220">
+        <v>0.97</v>
+      </c>
+      <c r="E36" s="220">
+        <v>0.95</v>
+      </c>
+      <c r="F36" s="220">
+        <v>0.95</v>
+      </c>
+      <c r="G36" s="220">
+        <v>0.95</v>
+      </c>
+      <c r="H36" s="220">
+        <v>0.95</v>
+      </c>
+      <c r="I36" s="165"/>
+      <c r="K36" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A37" s="156" t="s">
+        <v>47</v>
+      </c>
+      <c r="B37" s="220"/>
+      <c r="C37" s="220"/>
+      <c r="D37" s="220"/>
+      <c r="E37" s="220"/>
+      <c r="F37" s="220"/>
+      <c r="G37" s="220"/>
+      <c r="H37" s="220"/>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A38" s="156" t="s">
+        <v>48</v>
+      </c>
+      <c r="B38" s="220">
+        <v>0.99</v>
+      </c>
+      <c r="C38" s="220">
+        <v>0.99</v>
+      </c>
+      <c r="D38" s="220">
+        <v>0.99</v>
+      </c>
+      <c r="E38" s="220">
+        <v>0.99</v>
+      </c>
+      <c r="F38" s="220">
+        <v>0.99</v>
+      </c>
+      <c r="G38" s="220">
+        <v>0.99</v>
+      </c>
+      <c r="H38" s="220">
+        <v>0.99</v>
+      </c>
+      <c r="K38" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A39" s="156" t="s">
+        <v>49</v>
+      </c>
+      <c r="B39" s="220"/>
+      <c r="C39" s="220"/>
+      <c r="D39" s="220"/>
+      <c r="E39" s="220"/>
+      <c r="F39" s="220"/>
+      <c r="G39" s="220"/>
+      <c r="H39" s="220"/>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A40" s="156" t="s">
+        <v>50</v>
+      </c>
+      <c r="B40" s="220"/>
+      <c r="C40" s="220"/>
+      <c r="D40" s="220"/>
+      <c r="E40" s="220"/>
+      <c r="F40" s="220"/>
+      <c r="G40" s="220"/>
+      <c r="H40" s="220"/>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A41" s="156" t="s">
+        <v>51</v>
+      </c>
+      <c r="B41" s="220"/>
+      <c r="C41" s="220"/>
+      <c r="D41" s="220"/>
+      <c r="E41" s="220"/>
+      <c r="F41" s="220"/>
+      <c r="G41" s="220"/>
+      <c r="H41" s="220"/>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A42" s="157" t="s">
+        <v>52</v>
+      </c>
+      <c r="B42" s="220">
+        <v>0.99</v>
+      </c>
+      <c r="C42" s="220">
+        <v>0.99</v>
+      </c>
+      <c r="D42" s="220">
+        <v>0.99</v>
+      </c>
+      <c r="E42" s="220">
+        <v>0.99</v>
+      </c>
+      <c r="F42" s="220">
+        <v>0.99</v>
+      </c>
+      <c r="G42" s="220">
+        <v>0.99</v>
+      </c>
+      <c r="H42" s="220">
+        <v>0.99</v>
+      </c>
+      <c r="K42" t="s">
+        <v>280</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="K2" r:id="rId1" xr:uid="{65D74975-49E6-5244-9105-05CE933E5698}"/>
+    <hyperlink ref="L9" r:id="rId2" xr:uid="{3654E389-D7E1-C44E-8707-412BDAE01970}"/>
+    <hyperlink ref="L11" r:id="rId3" xr:uid="{94286478-0B97-C249-9837-9E0C1E5EB92D}"/>
+    <hyperlink ref="K32" r:id="rId4" xr:uid="{647C2F64-9640-BE41-9743-31C934244A34}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <tabColor rgb="FFFFF2CC"/>
@@ -5738,7 +7023,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
     <tabColor rgb="FFFFF2CC"/>
@@ -7248,7 +8533,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr>
     <tabColor theme="7" tint="0.79998168889431442"/>
@@ -8518,7 +9803,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <sheetPr>
     <tabColor rgb="FFD9D9D9"/>
@@ -8542,19 +9827,19 @@
       <c r="B1" s="90" t="s">
         <v>181</v>
       </c>
-      <c r="C1" s="211" t="s">
+      <c r="C1" s="210" t="s">
         <v>97</v>
       </c>
-      <c r="D1" s="211"/>
+      <c r="D1" s="210"/>
       <c r="E1" s="91" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="210" t="s">
+      <c r="A2" s="209" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="212" t="s">
+      <c r="B2" s="211" t="s">
         <v>182</v>
       </c>
       <c r="C2" s="92" t="s">
@@ -8568,8 +9853,8 @@
       </c>
     </row>
     <row r="3" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="210"/>
-      <c r="B3" s="212"/>
+      <c r="A3" s="209"/>
+      <c r="B3" s="211"/>
       <c r="C3" s="92" t="s">
         <v>104</v>
       </c>
@@ -8579,8 +9864,8 @@
       <c r="E3" s="93"/>
     </row>
     <row r="4" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="210"/>
-      <c r="B4" s="212"/>
+      <c r="A4" s="209"/>
+      <c r="B4" s="211"/>
       <c r="C4" s="92" t="s">
         <v>120</v>
       </c>
@@ -8590,8 +9875,8 @@
       <c r="E4" s="93"/>
     </row>
     <row r="5" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="210"/>
-      <c r="B5" s="212"/>
+      <c r="A5" s="209"/>
+      <c r="B5" s="211"/>
       <c r="C5" s="92" t="s">
         <v>122</v>
       </c>
@@ -8601,8 +9886,8 @@
       <c r="E5" s="93"/>
     </row>
     <row r="6" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="210"/>
-      <c r="B6" s="212"/>
+      <c r="A6" s="209"/>
+      <c r="B6" s="211"/>
       <c r="C6" s="92" t="s">
         <v>107</v>
       </c>
@@ -8612,8 +9897,8 @@
       <c r="E6" s="93"/>
     </row>
     <row r="7" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="210"/>
-      <c r="B7" s="212"/>
+      <c r="A7" s="209"/>
+      <c r="B7" s="211"/>
       <c r="C7" s="92" t="s">
         <v>188</v>
       </c>
@@ -8623,8 +9908,8 @@
       <c r="E7" s="93"/>
     </row>
     <row r="8" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="210"/>
-      <c r="B8" s="212"/>
+      <c r="A8" s="209"/>
+      <c r="B8" s="211"/>
       <c r="C8" s="92" t="s">
         <v>250</v>
       </c>
@@ -8636,7 +9921,7 @@
       </c>
     </row>
     <row r="9" spans="1:5" s="14" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="210"/>
+      <c r="A9" s="209"/>
       <c r="B9" s="159" t="s">
         <v>190</v>
       </c>
@@ -8651,8 +9936,8 @@
       </c>
     </row>
     <row r="10" spans="1:5" s="14" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="210"/>
-      <c r="B10" s="212" t="s">
+      <c r="A10" s="209"/>
+      <c r="B10" s="211" t="s">
         <v>192</v>
       </c>
       <c r="C10" s="92" t="s">
@@ -8664,8 +9949,8 @@
       <c r="E10" s="93"/>
     </row>
     <row r="11" spans="1:5" s="14" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="210"/>
-      <c r="B11" s="212"/>
+      <c r="A11" s="209"/>
+      <c r="B11" s="211"/>
       <c r="C11" s="92" t="s">
         <v>194</v>
       </c>
@@ -8675,8 +9960,8 @@
       <c r="E11" s="93"/>
     </row>
     <row r="12" spans="1:5" s="14" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="210"/>
-      <c r="B12" s="212"/>
+      <c r="A12" s="209"/>
+      <c r="B12" s="211"/>
       <c r="C12" s="92" t="s">
         <v>196</v>
       </c>
@@ -8686,8 +9971,8 @@
       <c r="E12" s="93"/>
     </row>
     <row r="13" spans="1:5" s="14" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="210"/>
-      <c r="B13" s="212"/>
+      <c r="A13" s="209"/>
+      <c r="B13" s="211"/>
       <c r="C13" s="92" t="s">
         <v>198</v>
       </c>
@@ -8697,8 +9982,8 @@
       <c r="E13" s="93"/>
     </row>
     <row r="14" spans="1:5" s="14" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="210"/>
-      <c r="B14" s="212"/>
+      <c r="A14" s="209"/>
+      <c r="B14" s="211"/>
       <c r="C14" s="92" t="s">
         <v>200</v>
       </c>
@@ -8708,8 +9993,8 @@
       <c r="E14" s="93"/>
     </row>
     <row r="15" spans="1:5" s="14" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="210"/>
-      <c r="B15" s="212"/>
+      <c r="A15" s="209"/>
+      <c r="B15" s="211"/>
       <c r="C15" s="92" t="s">
         <v>201</v>
       </c>
@@ -8719,8 +10004,8 @@
       <c r="E15" s="93"/>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="210"/>
-      <c r="B16" s="212"/>
+      <c r="A16" s="209"/>
+      <c r="B16" s="211"/>
       <c r="C16" s="92" t="s">
         <v>203</v>
       </c>
@@ -8730,10 +10015,10 @@
       <c r="E16" s="93"/>
     </row>
     <row r="17" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="210" t="s">
+      <c r="A17" s="209" t="s">
         <v>6</v>
       </c>
-      <c r="B17" s="212" t="s">
+      <c r="B17" s="211" t="s">
         <v>206</v>
       </c>
       <c r="C17" s="92" t="s">
@@ -8747,8 +10032,8 @@
       </c>
     </row>
     <row r="18" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="210"/>
-      <c r="B18" s="212"/>
+      <c r="A18" s="209"/>
+      <c r="B18" s="211"/>
       <c r="C18" s="92" t="s">
         <v>167</v>
       </c>
@@ -8758,8 +10043,8 @@
       <c r="E18" s="93"/>
     </row>
     <row r="19" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="210"/>
-      <c r="B19" s="212"/>
+      <c r="A19" s="209"/>
+      <c r="B19" s="211"/>
       <c r="C19" s="92" t="s">
         <v>208</v>
       </c>
@@ -8769,8 +10054,8 @@
       <c r="E19" s="93"/>
     </row>
     <row r="20" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="210"/>
-      <c r="B20" s="212"/>
+      <c r="A20" s="209"/>
+      <c r="B20" s="211"/>
       <c r="C20" s="92" t="s">
         <v>210</v>
       </c>
@@ -8780,8 +10065,8 @@
       <c r="E20" s="93"/>
     </row>
     <row r="21" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="210"/>
-      <c r="B21" s="212"/>
+      <c r="A21" s="209"/>
+      <c r="B21" s="211"/>
       <c r="C21" s="92" t="s">
         <v>211</v>
       </c>
@@ -8791,8 +10076,8 @@
       <c r="E21" s="93"/>
     </row>
     <row r="22" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="210"/>
-      <c r="B22" s="212" t="s">
+      <c r="A22" s="209"/>
+      <c r="B22" s="211" t="s">
         <v>213</v>
       </c>
       <c r="C22" s="92" t="s">
@@ -8806,8 +10091,8 @@
       </c>
     </row>
     <row r="23" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="210"/>
-      <c r="B23" s="212"/>
+      <c r="A23" s="209"/>
+      <c r="B23" s="211"/>
       <c r="C23" s="92" t="s">
         <v>168</v>
       </c>
@@ -8879,7 +10164,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <sheetPr>
     <tabColor rgb="FFD9D9D9"/>
@@ -8909,245 +10194,245 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:233" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C1" s="217" t="s">
+      <c r="C1" s="216" t="s">
         <v>216</v>
       </c>
-      <c r="D1" s="217"/>
-      <c r="E1" s="217"/>
-      <c r="F1" s="217"/>
-      <c r="G1" s="217"/>
-      <c r="H1" s="217"/>
-      <c r="I1" s="217"/>
-      <c r="J1" s="217"/>
-      <c r="K1" s="217"/>
-      <c r="L1" s="217"/>
-      <c r="M1" s="217"/>
-      <c r="N1" s="217"/>
-      <c r="O1" s="217"/>
-      <c r="P1" s="217"/>
-      <c r="Q1" s="217"/>
-      <c r="R1" s="217"/>
-      <c r="S1" s="217"/>
-      <c r="T1" s="217"/>
-      <c r="U1" s="217"/>
-      <c r="V1" s="217"/>
-      <c r="W1" s="217"/>
-      <c r="X1" s="217"/>
-      <c r="Y1" s="217"/>
-      <c r="Z1" s="217"/>
-      <c r="AA1" s="217"/>
-      <c r="AB1" s="217"/>
-      <c r="AC1" s="217"/>
-      <c r="AD1" s="217"/>
-      <c r="AE1" s="217"/>
-      <c r="AF1" s="217"/>
-      <c r="AG1" s="217"/>
-      <c r="AH1" s="217"/>
-      <c r="AI1" s="217"/>
-      <c r="AJ1" s="217"/>
-      <c r="AK1" s="217"/>
-      <c r="AL1" s="217"/>
-      <c r="AM1" s="217"/>
-      <c r="AN1" s="217"/>
-      <c r="AO1" s="217"/>
-      <c r="AP1" s="217"/>
-      <c r="AQ1" s="217"/>
-      <c r="AR1" s="217"/>
-      <c r="AS1" s="217"/>
-      <c r="AT1" s="217"/>
-      <c r="AU1" s="217"/>
-      <c r="AV1" s="217"/>
-      <c r="AW1" s="217"/>
-      <c r="AX1" s="217"/>
-      <c r="AY1" s="217"/>
-      <c r="AZ1" s="217"/>
-      <c r="BA1" s="217"/>
-      <c r="BB1" s="217"/>
-      <c r="BC1" s="217"/>
-      <c r="BD1" s="217"/>
-      <c r="BE1" s="217"/>
-      <c r="BF1" s="217"/>
-      <c r="BG1" s="217"/>
-      <c r="BH1" s="217"/>
-      <c r="BI1" s="217"/>
-      <c r="BJ1" s="217"/>
-      <c r="BK1" s="217"/>
-      <c r="BL1" s="217"/>
-      <c r="BM1" s="217"/>
-      <c r="BN1" s="217"/>
-      <c r="BO1" s="217"/>
-      <c r="BP1" s="217"/>
-      <c r="BQ1" s="217"/>
-      <c r="BR1" s="217"/>
-      <c r="BS1" s="217"/>
-      <c r="BT1" s="217"/>
-      <c r="BU1" s="217"/>
-      <c r="BV1" s="217"/>
-      <c r="BW1" s="217"/>
-      <c r="BX1" s="217"/>
-      <c r="BY1" s="217"/>
-      <c r="BZ1" s="217"/>
-      <c r="CA1" s="217"/>
-      <c r="CB1" s="217"/>
-      <c r="CC1" s="217"/>
-      <c r="CD1" s="217"/>
-      <c r="CE1" s="217"/>
-      <c r="CF1" s="217"/>
-      <c r="CG1" s="217"/>
-      <c r="CH1" s="217"/>
-      <c r="CI1" s="217"/>
-      <c r="CJ1" s="217"/>
-      <c r="CK1" s="217"/>
-      <c r="CL1" s="217"/>
-      <c r="CM1" s="217"/>
-      <c r="CN1" s="217"/>
-      <c r="CO1" s="217"/>
-      <c r="CP1" s="217"/>
-      <c r="CQ1" s="217"/>
-      <c r="CR1" s="217"/>
-      <c r="CS1" s="217"/>
-      <c r="CT1" s="217"/>
-      <c r="CU1" s="217"/>
-      <c r="CV1" s="217"/>
-      <c r="CW1" s="217"/>
-      <c r="CX1" s="217"/>
-      <c r="CY1" s="217"/>
-      <c r="CZ1" s="217"/>
-      <c r="DA1" s="217"/>
-      <c r="DB1" s="217"/>
-      <c r="DC1" s="217"/>
-      <c r="DD1" s="217"/>
-      <c r="DE1" s="217"/>
-      <c r="DF1" s="217"/>
-      <c r="DG1" s="217"/>
-      <c r="DJ1" s="216" t="s">
+      <c r="D1" s="216"/>
+      <c r="E1" s="216"/>
+      <c r="F1" s="216"/>
+      <c r="G1" s="216"/>
+      <c r="H1" s="216"/>
+      <c r="I1" s="216"/>
+      <c r="J1" s="216"/>
+      <c r="K1" s="216"/>
+      <c r="L1" s="216"/>
+      <c r="M1" s="216"/>
+      <c r="N1" s="216"/>
+      <c r="O1" s="216"/>
+      <c r="P1" s="216"/>
+      <c r="Q1" s="216"/>
+      <c r="R1" s="216"/>
+      <c r="S1" s="216"/>
+      <c r="T1" s="216"/>
+      <c r="U1" s="216"/>
+      <c r="V1" s="216"/>
+      <c r="W1" s="216"/>
+      <c r="X1" s="216"/>
+      <c r="Y1" s="216"/>
+      <c r="Z1" s="216"/>
+      <c r="AA1" s="216"/>
+      <c r="AB1" s="216"/>
+      <c r="AC1" s="216"/>
+      <c r="AD1" s="216"/>
+      <c r="AE1" s="216"/>
+      <c r="AF1" s="216"/>
+      <c r="AG1" s="216"/>
+      <c r="AH1" s="216"/>
+      <c r="AI1" s="216"/>
+      <c r="AJ1" s="216"/>
+      <c r="AK1" s="216"/>
+      <c r="AL1" s="216"/>
+      <c r="AM1" s="216"/>
+      <c r="AN1" s="216"/>
+      <c r="AO1" s="216"/>
+      <c r="AP1" s="216"/>
+      <c r="AQ1" s="216"/>
+      <c r="AR1" s="216"/>
+      <c r="AS1" s="216"/>
+      <c r="AT1" s="216"/>
+      <c r="AU1" s="216"/>
+      <c r="AV1" s="216"/>
+      <c r="AW1" s="216"/>
+      <c r="AX1" s="216"/>
+      <c r="AY1" s="216"/>
+      <c r="AZ1" s="216"/>
+      <c r="BA1" s="216"/>
+      <c r="BB1" s="216"/>
+      <c r="BC1" s="216"/>
+      <c r="BD1" s="216"/>
+      <c r="BE1" s="216"/>
+      <c r="BF1" s="216"/>
+      <c r="BG1" s="216"/>
+      <c r="BH1" s="216"/>
+      <c r="BI1" s="216"/>
+      <c r="BJ1" s="216"/>
+      <c r="BK1" s="216"/>
+      <c r="BL1" s="216"/>
+      <c r="BM1" s="216"/>
+      <c r="BN1" s="216"/>
+      <c r="BO1" s="216"/>
+      <c r="BP1" s="216"/>
+      <c r="BQ1" s="216"/>
+      <c r="BR1" s="216"/>
+      <c r="BS1" s="216"/>
+      <c r="BT1" s="216"/>
+      <c r="BU1" s="216"/>
+      <c r="BV1" s="216"/>
+      <c r="BW1" s="216"/>
+      <c r="BX1" s="216"/>
+      <c r="BY1" s="216"/>
+      <c r="BZ1" s="216"/>
+      <c r="CA1" s="216"/>
+      <c r="CB1" s="216"/>
+      <c r="CC1" s="216"/>
+      <c r="CD1" s="216"/>
+      <c r="CE1" s="216"/>
+      <c r="CF1" s="216"/>
+      <c r="CG1" s="216"/>
+      <c r="CH1" s="216"/>
+      <c r="CI1" s="216"/>
+      <c r="CJ1" s="216"/>
+      <c r="CK1" s="216"/>
+      <c r="CL1" s="216"/>
+      <c r="CM1" s="216"/>
+      <c r="CN1" s="216"/>
+      <c r="CO1" s="216"/>
+      <c r="CP1" s="216"/>
+      <c r="CQ1" s="216"/>
+      <c r="CR1" s="216"/>
+      <c r="CS1" s="216"/>
+      <c r="CT1" s="216"/>
+      <c r="CU1" s="216"/>
+      <c r="CV1" s="216"/>
+      <c r="CW1" s="216"/>
+      <c r="CX1" s="216"/>
+      <c r="CY1" s="216"/>
+      <c r="CZ1" s="216"/>
+      <c r="DA1" s="216"/>
+      <c r="DB1" s="216"/>
+      <c r="DC1" s="216"/>
+      <c r="DD1" s="216"/>
+      <c r="DE1" s="216"/>
+      <c r="DF1" s="216"/>
+      <c r="DG1" s="216"/>
+      <c r="DJ1" s="215" t="s">
         <v>217</v>
       </c>
-      <c r="DK1" s="216"/>
-      <c r="DL1" s="216"/>
-      <c r="DM1" s="216"/>
-      <c r="DN1" s="216"/>
-      <c r="DO1" s="216"/>
-      <c r="DP1" s="216"/>
-      <c r="DQ1" s="216"/>
-      <c r="DR1" s="216"/>
-      <c r="DS1" s="216"/>
-      <c r="DT1" s="216"/>
-      <c r="DU1" s="216"/>
-      <c r="DV1" s="216"/>
-      <c r="DW1" s="216"/>
-      <c r="DX1" s="216"/>
-      <c r="DY1" s="216"/>
-      <c r="DZ1" s="216"/>
-      <c r="EA1" s="216"/>
-      <c r="EB1" s="216"/>
-      <c r="EC1" s="216"/>
-      <c r="ED1" s="216"/>
-      <c r="EE1" s="216"/>
-      <c r="EF1" s="216"/>
-      <c r="EG1" s="216"/>
-      <c r="EH1" s="216"/>
-      <c r="EI1" s="216"/>
-      <c r="EJ1" s="216"/>
-      <c r="EK1" s="216"/>
-      <c r="EL1" s="216"/>
-      <c r="EM1" s="216"/>
-      <c r="EN1" s="216"/>
-      <c r="EO1" s="216"/>
-      <c r="EP1" s="216"/>
-      <c r="EQ1" s="216"/>
-      <c r="ER1" s="216"/>
-      <c r="ES1" s="216"/>
-      <c r="ET1" s="216"/>
-      <c r="EU1" s="216"/>
-      <c r="EV1" s="216"/>
-      <c r="EW1" s="216"/>
-      <c r="EX1" s="216"/>
-      <c r="EY1" s="216"/>
-      <c r="EZ1" s="216"/>
-      <c r="FA1" s="216"/>
-      <c r="FB1" s="216"/>
-      <c r="FC1" s="216"/>
-      <c r="FD1" s="216"/>
-      <c r="FE1" s="216"/>
-      <c r="FF1" s="216"/>
-      <c r="FG1" s="216"/>
-      <c r="FH1" s="216"/>
-      <c r="FI1" s="216"/>
-      <c r="FJ1" s="216"/>
-      <c r="FK1" s="216"/>
-      <c r="FL1" s="216"/>
-      <c r="FM1" s="216"/>
-      <c r="FN1" s="216"/>
-      <c r="FO1" s="216"/>
-      <c r="FP1" s="216"/>
-      <c r="FQ1" s="216"/>
-      <c r="FR1" s="216"/>
-      <c r="FS1" s="216"/>
-      <c r="FT1" s="216"/>
-      <c r="FU1" s="216"/>
-      <c r="FV1" s="216"/>
-      <c r="FW1" s="216"/>
-      <c r="FX1" s="216"/>
-      <c r="FY1" s="216"/>
-      <c r="FZ1" s="216"/>
-      <c r="GA1" s="216"/>
-      <c r="GB1" s="216"/>
-      <c r="GC1" s="216"/>
-      <c r="GD1" s="216"/>
-      <c r="GE1" s="216"/>
-      <c r="GF1" s="216"/>
-      <c r="GG1" s="216"/>
-      <c r="GH1" s="216"/>
-      <c r="GI1" s="216"/>
-      <c r="GJ1" s="216"/>
-      <c r="GK1" s="216"/>
-      <c r="GL1" s="216"/>
-      <c r="GM1" s="216"/>
-      <c r="GN1" s="216"/>
-      <c r="GO1" s="216"/>
-      <c r="GP1" s="216"/>
-      <c r="GQ1" s="216"/>
-      <c r="GR1" s="216"/>
-      <c r="GS1" s="216"/>
-      <c r="GT1" s="216"/>
-      <c r="GU1" s="216"/>
-      <c r="GV1" s="216"/>
-      <c r="GW1" s="216"/>
-      <c r="GX1" s="216"/>
-      <c r="GY1" s="216"/>
-      <c r="GZ1" s="216"/>
-      <c r="HA1" s="216"/>
-      <c r="HB1" s="216"/>
-      <c r="HC1" s="216"/>
-      <c r="HD1" s="216"/>
-      <c r="HE1" s="216"/>
-      <c r="HF1" s="216"/>
-      <c r="HG1" s="216"/>
-      <c r="HH1" s="216"/>
-      <c r="HI1" s="216"/>
-      <c r="HJ1" s="216"/>
-      <c r="HK1" s="216"/>
-      <c r="HL1" s="216"/>
-      <c r="HM1" s="216"/>
-      <c r="HN1" s="216"/>
-      <c r="HP1" s="219" t="s">
+      <c r="DK1" s="215"/>
+      <c r="DL1" s="215"/>
+      <c r="DM1" s="215"/>
+      <c r="DN1" s="215"/>
+      <c r="DO1" s="215"/>
+      <c r="DP1" s="215"/>
+      <c r="DQ1" s="215"/>
+      <c r="DR1" s="215"/>
+      <c r="DS1" s="215"/>
+      <c r="DT1" s="215"/>
+      <c r="DU1" s="215"/>
+      <c r="DV1" s="215"/>
+      <c r="DW1" s="215"/>
+      <c r="DX1" s="215"/>
+      <c r="DY1" s="215"/>
+      <c r="DZ1" s="215"/>
+      <c r="EA1" s="215"/>
+      <c r="EB1" s="215"/>
+      <c r="EC1" s="215"/>
+      <c r="ED1" s="215"/>
+      <c r="EE1" s="215"/>
+      <c r="EF1" s="215"/>
+      <c r="EG1" s="215"/>
+      <c r="EH1" s="215"/>
+      <c r="EI1" s="215"/>
+      <c r="EJ1" s="215"/>
+      <c r="EK1" s="215"/>
+      <c r="EL1" s="215"/>
+      <c r="EM1" s="215"/>
+      <c r="EN1" s="215"/>
+      <c r="EO1" s="215"/>
+      <c r="EP1" s="215"/>
+      <c r="EQ1" s="215"/>
+      <c r="ER1" s="215"/>
+      <c r="ES1" s="215"/>
+      <c r="ET1" s="215"/>
+      <c r="EU1" s="215"/>
+      <c r="EV1" s="215"/>
+      <c r="EW1" s="215"/>
+      <c r="EX1" s="215"/>
+      <c r="EY1" s="215"/>
+      <c r="EZ1" s="215"/>
+      <c r="FA1" s="215"/>
+      <c r="FB1" s="215"/>
+      <c r="FC1" s="215"/>
+      <c r="FD1" s="215"/>
+      <c r="FE1" s="215"/>
+      <c r="FF1" s="215"/>
+      <c r="FG1" s="215"/>
+      <c r="FH1" s="215"/>
+      <c r="FI1" s="215"/>
+      <c r="FJ1" s="215"/>
+      <c r="FK1" s="215"/>
+      <c r="FL1" s="215"/>
+      <c r="FM1" s="215"/>
+      <c r="FN1" s="215"/>
+      <c r="FO1" s="215"/>
+      <c r="FP1" s="215"/>
+      <c r="FQ1" s="215"/>
+      <c r="FR1" s="215"/>
+      <c r="FS1" s="215"/>
+      <c r="FT1" s="215"/>
+      <c r="FU1" s="215"/>
+      <c r="FV1" s="215"/>
+      <c r="FW1" s="215"/>
+      <c r="FX1" s="215"/>
+      <c r="FY1" s="215"/>
+      <c r="FZ1" s="215"/>
+      <c r="GA1" s="215"/>
+      <c r="GB1" s="215"/>
+      <c r="GC1" s="215"/>
+      <c r="GD1" s="215"/>
+      <c r="GE1" s="215"/>
+      <c r="GF1" s="215"/>
+      <c r="GG1" s="215"/>
+      <c r="GH1" s="215"/>
+      <c r="GI1" s="215"/>
+      <c r="GJ1" s="215"/>
+      <c r="GK1" s="215"/>
+      <c r="GL1" s="215"/>
+      <c r="GM1" s="215"/>
+      <c r="GN1" s="215"/>
+      <c r="GO1" s="215"/>
+      <c r="GP1" s="215"/>
+      <c r="GQ1" s="215"/>
+      <c r="GR1" s="215"/>
+      <c r="GS1" s="215"/>
+      <c r="GT1" s="215"/>
+      <c r="GU1" s="215"/>
+      <c r="GV1" s="215"/>
+      <c r="GW1" s="215"/>
+      <c r="GX1" s="215"/>
+      <c r="GY1" s="215"/>
+      <c r="GZ1" s="215"/>
+      <c r="HA1" s="215"/>
+      <c r="HB1" s="215"/>
+      <c r="HC1" s="215"/>
+      <c r="HD1" s="215"/>
+      <c r="HE1" s="215"/>
+      <c r="HF1" s="215"/>
+      <c r="HG1" s="215"/>
+      <c r="HH1" s="215"/>
+      <c r="HI1" s="215"/>
+      <c r="HJ1" s="215"/>
+      <c r="HK1" s="215"/>
+      <c r="HL1" s="215"/>
+      <c r="HM1" s="215"/>
+      <c r="HN1" s="215"/>
+      <c r="HP1" s="218" t="s">
         <v>218</v>
       </c>
-      <c r="HQ1" s="219"/>
-      <c r="HR1" s="219"/>
-      <c r="HS1" s="218" t="s">
+      <c r="HQ1" s="218"/>
+      <c r="HR1" s="218"/>
+      <c r="HS1" s="217" t="s">
         <v>219</v>
       </c>
-      <c r="HT1" s="218"/>
-      <c r="HU1" s="218"/>
-      <c r="HW1" s="215" t="s">
+      <c r="HT1" s="217"/>
+      <c r="HU1" s="217"/>
+      <c r="HW1" s="214" t="s">
         <v>93</v>
       </c>
-      <c r="HX1" s="214" t="s">
+      <c r="HX1" s="213" t="s">
         <v>99</v>
       </c>
-      <c r="HY1" s="215" t="s">
+      <c r="HY1" s="214" t="s">
         <v>100</v>
       </c>
     </row>
@@ -9833,9 +11118,9 @@
       <c r="HU2" s="184" t="s">
         <v>108</v>
       </c>
-      <c r="HW2" s="215"/>
-      <c r="HX2" s="215"/>
-      <c r="HY2" s="215"/>
+      <c r="HW2" s="214"/>
+      <c r="HX2" s="214"/>
+      <c r="HY2" s="214"/>
     </row>
     <row r="3" spans="1:233" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
@@ -31156,22 +32441,22 @@
       <c r="HJ42" s="52"/>
     </row>
     <row r="43" spans="1:233" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="213" t="s">
+      <c r="A43" s="212" t="s">
         <v>227</v>
       </c>
-      <c r="B43" s="213"/>
-      <c r="C43" s="213"/>
-      <c r="D43" s="213"/>
-      <c r="E43" s="213"/>
-      <c r="F43" s="213"/>
-      <c r="G43" s="213"/>
-      <c r="H43" s="213"/>
-      <c r="I43" s="213"/>
-      <c r="J43" s="213"/>
-      <c r="K43" s="213"/>
-      <c r="L43" s="213"/>
-      <c r="M43" s="213"/>
-      <c r="N43" s="213"/>
+      <c r="B43" s="212"/>
+      <c r="C43" s="212"/>
+      <c r="D43" s="212"/>
+      <c r="E43" s="212"/>
+      <c r="F43" s="212"/>
+      <c r="G43" s="212"/>
+      <c r="H43" s="212"/>
+      <c r="I43" s="212"/>
+      <c r="J43" s="212"/>
+      <c r="K43" s="212"/>
+      <c r="L43" s="212"/>
+      <c r="M43" s="212"/>
+      <c r="N43" s="212"/>
     </row>
     <row r="44" spans="1:233" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="82"/>
